--- a/VM2026_Tipping_Stig.xlsx
+++ b/VM2026_Tipping_Stig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://consafelogistics-my.sharepoint.com/personal/martin_skaug_consafelogistics_com/Documents/Desktop/VM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://consafelogistics-my.sharepoint.com/personal/martin_skaug_consafelogistics_com/Documents/Desktop/VM/Tipping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5DCC8D5-9F03-4F08-8C4D-B06D4EEBDECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{E5DCC8D5-9F03-4F08-8C4D-B06D4EEBDECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B17E1757-AC9D-411F-8830-4BEFF5CFD03E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="169">
   <si>
     <t>⚽  VM 2026  –  MINE TIPS</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Ditt navn:</t>
-  </si>
-  <si>
-    <t>The Stig</t>
   </si>
   <si>
     <t>🟢 = 1. plass  •  🟡 = 2. plass   →  videre til sluttspill</t>
@@ -545,10 +542,10 @@
     <t xml:space="preserve">  FINALE  —  velg vinneren  🏆</t>
   </si>
   <si>
-    <t>argentina</t>
+    <t>Makedonia</t>
   </si>
   <si>
-    <t>Makedonia</t>
+    <t>Stig</t>
   </si>
 </sst>
 </file>
@@ -558,7 +555,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\✓;;;\□"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1349,7 +1346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1491,9 +1488,6 @@
     </xf>
     <xf numFmtId="164" fontId="23" fillId="34" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="34" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2097,20 +2091,20 @@
     <tabColor rgb="FFE94560"/>
   </sheetPr>
   <dimension ref="A1:AF367"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" customWidth="1"/>
-    <col min="12" max="12" width="1.5703125" customWidth="1"/>
+    <col min="11" max="11" width="6.88671875" customWidth="1"/>
+    <col min="12" max="12" width="1.5546875" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
     <col min="14" max="17" width="4" customWidth="1"/>
     <col min="18" max="21" width="5" customWidth="1"/>
@@ -2118,206 +2112,206 @@
     <col min="23" max="32" width="18" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="36" customHeight="1">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:32" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="M1" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-    </row>
-    <row r="2" spans="1:32" ht="24" customHeight="1">
-      <c r="A2" s="67" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="68" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="M2" s="69" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="M1" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+    </row>
+    <row r="2" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="67" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="M2" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68"/>
+      <c r="S2" s="68"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="68"/>
+    </row>
+    <row r="3" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-    </row>
-    <row r="3" spans="1:32" ht="18" customHeight="1">
-      <c r="A3" s="63" t="s">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+      <c r="M3" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="M3" s="64" t="s">
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+    </row>
+    <row r="4" spans="1:32" ht="4.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
-      <c r="T3" s="64"/>
-      <c r="U3" s="64"/>
-    </row>
-    <row r="4" spans="1:32" ht="4.5" customHeight="1"/>
-    <row r="5" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A5" s="56" t="s">
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="M5" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="M5" s="57" t="s">
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+    </row>
+    <row r="6" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="57"/>
-      <c r="S5" s="57"/>
-      <c r="T5" s="57"/>
-      <c r="U5" s="57"/>
-    </row>
-    <row r="6" spans="1:32" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="M6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" ht="16.5" customHeight="1">
-      <c r="A7" s="3">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="5">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="K7" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="M7" s="4" t="str">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=1,W7,IF(AF8=1,W8,IF(AF9=1,W9,IF(AF10=1,W10,"")))),"")</f>
@@ -2356,7 +2350,7 @@
         <v>7</v>
       </c>
       <c r="W7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X7">
         <f>((C7="Mexico")*ISNUMBER(D7))+((G7="Mexico")*ISNUMBER(D7))+((C8="Mexico")*ISNUMBER(D8))+((G8="Mexico")*ISNUMBER(D8))+((C9="Mexico")*ISNUMBER(D9))+((G9="Mexico")*ISNUMBER(D9))+((C10="Mexico")*ISNUMBER(D10))+((G10="Mexico")*ISNUMBER(D10))+((C11="Mexico")*ISNUMBER(D11))+((G11="Mexico")*ISNUMBER(D11))+((C12="Mexico")*ISNUMBER(D12))+((G12="Mexico")*ISNUMBER(D12))</f>
@@ -2395,39 +2389,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="16.5" customHeight="1">
+    <row r="8" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>2</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="5">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="I8" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>41</v>
       </c>
       <c r="M8" s="4" t="str">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=2,W7,IF(AF8=2,W8,IF(AF9=2,W9,IF(AF10=2,W10,"")))),"")</f>
@@ -2466,7 +2460,7 @@
         <v>3</v>
       </c>
       <c r="W8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="X8">
         <f>((C7="Sør-Afrika")*ISNUMBER(D7))+((G7="Sør-Afrika")*ISNUMBER(D7))+((C8="Sør-Afrika")*ISNUMBER(D8))+((G8="Sør-Afrika")*ISNUMBER(D8))+((C9="Sør-Afrika")*ISNUMBER(D9))+((G9="Sør-Afrika")*ISNUMBER(D9))+((C10="Sør-Afrika")*ISNUMBER(D10))+((G10="Sør-Afrika")*ISNUMBER(D10))+((C11="Sør-Afrika")*ISNUMBER(D11))+((G11="Sør-Afrika")*ISNUMBER(D11))+((C12="Sør-Afrika")*ISNUMBER(D12))+((G12="Sør-Afrika")*ISNUMBER(D12))</f>
@@ -2505,39 +2499,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="16.5" customHeight="1">
+    <row r="9" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="5">
         <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="5">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="H9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="K9" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M9" s="4" t="str">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=3,W7,IF(AF8=3,W8,IF(AF9=3,W9,IF(AF10=3,W10,"")))),"")</f>
@@ -2576,7 +2570,7 @@
         <v>2</v>
       </c>
       <c r="W9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X9">
         <f>((C7="Sør-Korea")*ISNUMBER(D7))+((G7="Sør-Korea")*ISNUMBER(D7))+((C8="Sør-Korea")*ISNUMBER(D8))+((G8="Sør-Korea")*ISNUMBER(D8))+((C9="Sør-Korea")*ISNUMBER(D9))+((G9="Sør-Korea")*ISNUMBER(D9))+((C10="Sør-Korea")*ISNUMBER(D10))+((G10="Sør-Korea")*ISNUMBER(D10))+((C11="Sør-Korea")*ISNUMBER(D11))+((G11="Sør-Korea")*ISNUMBER(D11))+((C12="Sør-Korea")*ISNUMBER(D12))+((G12="Sør-Korea")*ISNUMBER(D12))</f>
@@ -2615,39 +2609,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="16.5" customHeight="1">
+    <row r="10" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>4</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="D10" s="5">
         <v>1</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="J10" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M10" s="4" t="str">
         <f>IF(AND(ISNUMBER(D7),ISNUMBER(D8),ISNUMBER(D9),ISNUMBER(D10),ISNUMBER(D11),ISNUMBER(D12)),IF(AF7=4,W7,IF(AF8=4,W8,IF(AF9=4,W9,IF(AF10=4,W10,"")))),"")</f>
@@ -2686,7 +2680,7 @@
         <v>2</v>
       </c>
       <c r="W10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X10">
         <f>((C7="Tsjekkia")*ISNUMBER(D7))+((G7="Tsjekkia")*ISNUMBER(D7))+((C8="Tsjekkia")*ISNUMBER(D8))+((G8="Tsjekkia")*ISNUMBER(D8))+((C9="Tsjekkia")*ISNUMBER(D9))+((G9="Tsjekkia")*ISNUMBER(D9))+((C10="Tsjekkia")*ISNUMBER(D10))+((G10="Tsjekkia")*ISNUMBER(D10))+((C11="Tsjekkia")*ISNUMBER(D11))+((G11="Tsjekkia")*ISNUMBER(D11))+((C12="Tsjekkia")*ISNUMBER(D12))+((G12="Tsjekkia")*ISNUMBER(D12))</f>
@@ -2725,195 +2719,195 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="16.5" customHeight="1">
+    <row r="11" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>5</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F11" s="5">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="12" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>6</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="5">
         <v>1</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="K12" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="K12" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A13" s="56" t="s">
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="M13" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="56"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="56"/>
-      <c r="M13" s="57" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="57"/>
-      <c r="O13" s="57"/>
-      <c r="P13" s="57"/>
-      <c r="Q13" s="57"/>
-      <c r="R13" s="57"/>
-      <c r="S13" s="57"/>
-      <c r="T13" s="57"/>
-      <c r="U13" s="57"/>
-    </row>
-    <row r="14" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="56"/>
+    </row>
+    <row r="14" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="M14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="U14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="15" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="D15" s="5">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" s="5">
         <v>0</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="K15" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M15" s="4" t="str">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=1,W15,IF(AF16=1,W16,IF(AF17=1,W17,IF(AF18=1,W18,"")))),"")</f>
@@ -2952,7 +2946,7 @@
         <v>9</v>
       </c>
       <c r="W15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X15">
         <f>((C15="Canada")*ISNUMBER(D15))+((G15="Canada")*ISNUMBER(D15))+((C16="Canada")*ISNUMBER(D16))+((G16="Canada")*ISNUMBER(D16))+((C17="Canada")*ISNUMBER(D17))+((G17="Canada")*ISNUMBER(D17))+((C18="Canada")*ISNUMBER(D18))+((G18="Canada")*ISNUMBER(D18))+((C19="Canada")*ISNUMBER(D19))+((G19="Canada")*ISNUMBER(D19))+((C20="Canada")*ISNUMBER(D20))+((G20="Canada")*ISNUMBER(D20))</f>
@@ -2991,39 +2985,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="16.5" customHeight="1">
+    <row r="16" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>8</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="5">
+        <v>2</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="5">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="5">
-        <v>2</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="I16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="K16" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M16" s="4" t="str">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=2,W15,IF(AF16=2,W16,IF(AF17=2,W17,IF(AF18=2,W18,"")))),"")</f>
@@ -3062,7 +3056,7 @@
         <v>4</v>
       </c>
       <c r="W16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="X16">
         <f>((C15="Bosnia-Hercegovina")*ISNUMBER(D15))+((G15="Bosnia-Hercegovina")*ISNUMBER(D15))+((C16="Bosnia-Hercegovina")*ISNUMBER(D16))+((G16="Bosnia-Hercegovina")*ISNUMBER(D16))+((C17="Bosnia-Hercegovina")*ISNUMBER(D17))+((G17="Bosnia-Hercegovina")*ISNUMBER(D17))+((C18="Bosnia-Hercegovina")*ISNUMBER(D18))+((G18="Bosnia-Hercegovina")*ISNUMBER(D18))+((C19="Bosnia-Hercegovina")*ISNUMBER(D19))+((G19="Bosnia-Hercegovina")*ISNUMBER(D19))+((C20="Bosnia-Hercegovina")*ISNUMBER(D20))+((G20="Bosnia-Hercegovina")*ISNUMBER(D20))</f>
@@ -3101,39 +3095,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="16.5" customHeight="1">
+    <row r="17" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>9</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D17" s="5">
         <v>3</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" s="5">
         <v>0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M17" s="4" t="str">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=3,W15,IF(AF16=3,W16,IF(AF17=3,W17,IF(AF18=3,W18,"")))),"")</f>
@@ -3172,7 +3166,7 @@
         <v>3</v>
       </c>
       <c r="W17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="X17">
         <f>((C15="Qatar")*ISNUMBER(D15))+((G15="Qatar")*ISNUMBER(D15))+((C16="Qatar")*ISNUMBER(D16))+((G16="Qatar")*ISNUMBER(D16))+((C17="Qatar")*ISNUMBER(D17))+((G17="Qatar")*ISNUMBER(D17))+((C18="Qatar")*ISNUMBER(D18))+((G18="Qatar")*ISNUMBER(D18))+((C19="Qatar")*ISNUMBER(D19))+((G19="Qatar")*ISNUMBER(D19))+((C20="Qatar")*ISNUMBER(D20))+((G20="Qatar")*ISNUMBER(D20))</f>
@@ -3211,39 +3205,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="16.5" customHeight="1">
+    <row r="18" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>10</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="D18" s="5">
         <v>1</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" s="5">
         <v>1</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J18" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="K18" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M18" s="4" t="str">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(D16),ISNUMBER(D17),ISNUMBER(D18),ISNUMBER(D19),ISNUMBER(D20)),IF(AF15=4,W15,IF(AF16=4,W16,IF(AF17=4,W17,IF(AF18=4,W18,"")))),"")</f>
@@ -3282,7 +3276,7 @@
         <v>1</v>
       </c>
       <c r="W18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="X18">
         <f>((C15="Sveits")*ISNUMBER(D15))+((G15="Sveits")*ISNUMBER(D15))+((C16="Sveits")*ISNUMBER(D16))+((G16="Sveits")*ISNUMBER(D16))+((C17="Sveits")*ISNUMBER(D17))+((G17="Sveits")*ISNUMBER(D17))+((C18="Sveits")*ISNUMBER(D18))+((G18="Sveits")*ISNUMBER(D18))+((C19="Sveits")*ISNUMBER(D19))+((G19="Sveits")*ISNUMBER(D19))+((C20="Sveits")*ISNUMBER(D20))+((G20="Sveits")*ISNUMBER(D20))</f>
@@ -3321,195 +3315,195 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="16.5" customHeight="1">
+    <row r="19" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>11</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="5">
-        <v>2</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F19" s="5">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="H19" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:32" ht="16.5" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>12</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20" s="5">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="8" t="s">
+      <c r="K20" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="K20" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A21" s="56" t="s">
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="M21" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="56"/>
-      <c r="M21" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="N21" s="57"/>
-      <c r="O21" s="57"/>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="57"/>
-      <c r="R21" s="57"/>
-      <c r="S21" s="57"/>
-      <c r="T21" s="57"/>
-      <c r="U21" s="57"/>
-    </row>
-    <row r="22" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N21" s="56"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="56"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="56"/>
+      <c r="U21" s="56"/>
+    </row>
+    <row r="22" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="M22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="S22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T22" s="2" t="s">
+      <c r="U22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U22" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="23" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>13</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="5">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="5">
-        <v>2</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F23" s="5">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J23" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="K23" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M23" s="4" t="str">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=1,W23,IF(AF24=1,W24,IF(AF25=1,W25,IF(AF26=1,W26,"")))),"")</f>
@@ -3548,7 +3542,7 @@
         <v>9</v>
       </c>
       <c r="W23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X23">
         <f>((C23="Brasil")*ISNUMBER(D23))+((G23="Brasil")*ISNUMBER(D23))+((C24="Brasil")*ISNUMBER(D24))+((G24="Brasil")*ISNUMBER(D24))+((C25="Brasil")*ISNUMBER(D25))+((G25="Brasil")*ISNUMBER(D25))+((C26="Brasil")*ISNUMBER(D26))+((G26="Brasil")*ISNUMBER(D26))+((C27="Brasil")*ISNUMBER(D27))+((G27="Brasil")*ISNUMBER(D27))+((C28="Brasil")*ISNUMBER(D28))+((G28="Brasil")*ISNUMBER(D28))</f>
@@ -3587,39 +3581,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="16.5" customHeight="1">
+    <row r="24" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>14</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="5">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="5">
-        <v>1</v>
-      </c>
-      <c r="G24" s="8" t="s">
+      <c r="H24" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="K24" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M24" s="4" t="str">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=2,W23,IF(AF24=2,W24,IF(AF25=2,W25,IF(AF26=2,W26,"")))),"")</f>
@@ -3658,7 +3652,7 @@
         <v>6</v>
       </c>
       <c r="W24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="X24">
         <f>((C23="Marokko")*ISNUMBER(D23))+((G23="Marokko")*ISNUMBER(D23))+((C24="Marokko")*ISNUMBER(D24))+((G24="Marokko")*ISNUMBER(D24))+((C25="Marokko")*ISNUMBER(D25))+((G25="Marokko")*ISNUMBER(D25))+((C26="Marokko")*ISNUMBER(D26))+((G26="Marokko")*ISNUMBER(D26))+((C27="Marokko")*ISNUMBER(D27))+((G27="Marokko")*ISNUMBER(D27))+((C28="Marokko")*ISNUMBER(D28))+((G28="Marokko")*ISNUMBER(D28))</f>
@@ -3697,39 +3691,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:32" ht="16.5" customHeight="1">
+    <row r="25" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>15</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="5">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J25" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D25" s="5">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" s="5">
-        <v>2</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="K25" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M25" s="4" t="str">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=3,W23,IF(AF24=3,W24,IF(AF25=3,W25,IF(AF26=3,W26,"")))),"")</f>
@@ -3768,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="W25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="X25">
         <f>((C23="Haiti")*ISNUMBER(D23))+((G23="Haiti")*ISNUMBER(D23))+((C24="Haiti")*ISNUMBER(D24))+((G24="Haiti")*ISNUMBER(D24))+((C25="Haiti")*ISNUMBER(D25))+((G25="Haiti")*ISNUMBER(D25))+((C26="Haiti")*ISNUMBER(D26))+((G26="Haiti")*ISNUMBER(D26))+((C27="Haiti")*ISNUMBER(D27))+((G27="Haiti")*ISNUMBER(D27))+((C28="Haiti")*ISNUMBER(D28))+((G28="Haiti")*ISNUMBER(D28))</f>
@@ -3807,39 +3801,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="16.5" customHeight="1">
+    <row r="26" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>16</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="D26" s="5">
         <v>3</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F26" s="5">
         <v>0</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H26" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="K26" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M26" s="4" t="str">
         <f>IF(AND(ISNUMBER(D23),ISNUMBER(D24),ISNUMBER(D25),ISNUMBER(D26),ISNUMBER(D27),ISNUMBER(D28)),IF(AF23=4,W23,IF(AF24=4,W24,IF(AF25=4,W25,IF(AF26=4,W26,"")))),"")</f>
@@ -3878,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="W26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="X26">
         <f>((C23="Skottland")*ISNUMBER(D23))+((G23="Skottland")*ISNUMBER(D23))+((C24="Skottland")*ISNUMBER(D24))+((G24="Skottland")*ISNUMBER(D24))+((C25="Skottland")*ISNUMBER(D25))+((G25="Skottland")*ISNUMBER(D25))+((C26="Skottland")*ISNUMBER(D26))+((G26="Skottland")*ISNUMBER(D26))+((C27="Skottland")*ISNUMBER(D27))+((G27="Skottland")*ISNUMBER(D27))+((C28="Skottland")*ISNUMBER(D28))+((G28="Skottland")*ISNUMBER(D28))</f>
@@ -3917,195 +3911,195 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:32" ht="16.5" customHeight="1">
+    <row r="27" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>17</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D27" s="5">
         <v>0</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27" s="5">
         <v>3</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:32" ht="16.5" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>18</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D28" s="5">
         <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28" s="5">
         <v>0</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A29" s="56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="55" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="55"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
+      <c r="K29" s="55"/>
+      <c r="M29" s="56" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="56"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="56"/>
-      <c r="M29" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="N29" s="57"/>
-      <c r="O29" s="57"/>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="57"/>
-      <c r="R29" s="57"/>
-      <c r="S29" s="57"/>
-      <c r="T29" s="57"/>
-      <c r="U29" s="57"/>
-    </row>
-    <row r="30" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N29" s="56"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="56"/>
+      <c r="R29" s="56"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="56"/>
+      <c r="U29" s="56"/>
+    </row>
+    <row r="30" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="M30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="Q30" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="R30" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R30" s="2" t="s">
+      <c r="S30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S30" s="2" t="s">
+      <c r="T30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T30" s="2" t="s">
+      <c r="U30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U30" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="31" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>19</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="5">
+        <v>1</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="5">
-        <v>1</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="5">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="H31" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M31" s="4" t="str">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=1,W31,IF(AF32=1,W32,IF(AF33=1,W33,IF(AF34=1,W34,"")))),"")</f>
@@ -4144,7 +4138,7 @@
         <v>7</v>
       </c>
       <c r="W31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="X31">
         <f>((C31="USA")*ISNUMBER(D31))+((G31="USA")*ISNUMBER(D31))+((C32="USA")*ISNUMBER(D32))+((G32="USA")*ISNUMBER(D32))+((C33="USA")*ISNUMBER(D33))+((G33="USA")*ISNUMBER(D33))+((C34="USA")*ISNUMBER(D34))+((G34="USA")*ISNUMBER(D34))+((C35="USA")*ISNUMBER(D35))+((G35="USA")*ISNUMBER(D35))+((C36="USA")*ISNUMBER(D36))+((G36="USA")*ISNUMBER(D36))</f>
@@ -4183,39 +4177,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:32" ht="16.5" customHeight="1">
+    <row r="32" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>20</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" s="5">
+        <v>1</v>
+      </c>
+      <c r="G32" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="5">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" s="5">
-        <v>1</v>
-      </c>
-      <c r="G32" s="8" t="s">
+      <c r="H32" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H32" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="J32" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M32" s="4" t="str">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=2,W31,IF(AF32=2,W32,IF(AF33=2,W33,IF(AF34=2,W34,"")))),"")</f>
@@ -4254,7 +4248,7 @@
         <v>5</v>
       </c>
       <c r="W32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="X32">
         <f>((C31="Paraguay")*ISNUMBER(D31))+((G31="Paraguay")*ISNUMBER(D31))+((C32="Paraguay")*ISNUMBER(D32))+((G32="Paraguay")*ISNUMBER(D32))+((C33="Paraguay")*ISNUMBER(D33))+((G33="Paraguay")*ISNUMBER(D33))+((C34="Paraguay")*ISNUMBER(D34))+((G34="Paraguay")*ISNUMBER(D34))+((C35="Paraguay")*ISNUMBER(D35))+((G35="Paraguay")*ISNUMBER(D35))+((C36="Paraguay")*ISNUMBER(D36))+((G36="Paraguay")*ISNUMBER(D36))</f>
@@ -4293,39 +4287,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:32" ht="16.5" customHeight="1">
+    <row r="33" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>21</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="D33" s="5">
         <v>1</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33" s="5">
         <v>2</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M33" s="4" t="str">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=3,W31,IF(AF32=3,W32,IF(AF33=3,W33,IF(AF34=3,W34,"")))),"")</f>
@@ -4364,7 +4358,7 @@
         <v>2</v>
       </c>
       <c r="W33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="X33">
         <f>((C31="Australia")*ISNUMBER(D31))+((G31="Australia")*ISNUMBER(D31))+((C32="Australia")*ISNUMBER(D32))+((G32="Australia")*ISNUMBER(D32))+((C33="Australia")*ISNUMBER(D33))+((G33="Australia")*ISNUMBER(D33))+((C34="Australia")*ISNUMBER(D34))+((G34="Australia")*ISNUMBER(D34))+((C35="Australia")*ISNUMBER(D35))+((G35="Australia")*ISNUMBER(D35))+((C36="Australia")*ISNUMBER(D36))+((G36="Australia")*ISNUMBER(D36))</f>
@@ -4403,39 +4397,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:32" ht="16.5" customHeight="1">
+    <row r="34" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>22</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D34" s="5">
         <v>2</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34" s="5">
         <v>0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M34" s="4" t="str">
         <f>IF(AND(ISNUMBER(D31),ISNUMBER(D32),ISNUMBER(D33),ISNUMBER(D34),ISNUMBER(D35),ISNUMBER(D36)),IF(AF31=4,W31,IF(AF32=4,W32,IF(AF33=4,W33,IF(AF34=4,W34,"")))),"")</f>
@@ -4474,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="W34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="X34">
         <f>((C31="Tyrkia")*ISNUMBER(D31))+((G31="Tyrkia")*ISNUMBER(D31))+((C32="Tyrkia")*ISNUMBER(D32))+((G32="Tyrkia")*ISNUMBER(D32))+((C33="Tyrkia")*ISNUMBER(D33))+((G33="Tyrkia")*ISNUMBER(D33))+((C34="Tyrkia")*ISNUMBER(D34))+((G34="Tyrkia")*ISNUMBER(D34))+((C35="Tyrkia")*ISNUMBER(D35))+((G35="Tyrkia")*ISNUMBER(D35))+((C36="Tyrkia")*ISNUMBER(D36))+((G36="Tyrkia")*ISNUMBER(D36))</f>
@@ -4513,195 +4507,195 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:32" ht="16.5" customHeight="1">
+    <row r="35" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>23</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35" s="5">
         <v>2</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:32" ht="16.5" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>24</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C36" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="5">
+        <v>1</v>
+      </c>
+      <c r="G36" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="5">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" s="5">
-        <v>1</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>83</v>
-      </c>
       <c r="H36" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A37" s="56" t="s">
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="55"/>
+      <c r="M37" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="56"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="56"/>
-      <c r="M37" s="57" t="s">
-        <v>88</v>
-      </c>
-      <c r="N37" s="57"/>
-      <c r="O37" s="57"/>
-      <c r="P37" s="57"/>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-    </row>
-    <row r="38" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N37" s="56"/>
+      <c r="O37" s="56"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="56"/>
+      <c r="R37" s="56"/>
+      <c r="S37" s="56"/>
+      <c r="T37" s="56"/>
+      <c r="U37" s="56"/>
+    </row>
+    <row r="38" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J38" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="M38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="P38" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="Q38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q38" s="2" t="s">
+      <c r="R38" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R38" s="2" t="s">
+      <c r="S38" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S38" s="2" t="s">
+      <c r="T38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T38" s="2" t="s">
+      <c r="U38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="39" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>25</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="D39" s="5">
         <v>3</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
       <c r="G39" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I39" s="3" t="s">
+      <c r="J39" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="K39" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M39" s="4" t="str">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=1,W39,IF(AF40=1,W40,IF(AF41=1,W41,IF(AF42=1,W42,"")))),"")</f>
@@ -4740,7 +4734,7 @@
         <v>9</v>
       </c>
       <c r="W39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="X39">
         <f>((C39="Tyskland")*ISNUMBER(D39))+((G39="Tyskland")*ISNUMBER(D39))+((C40="Tyskland")*ISNUMBER(D40))+((G40="Tyskland")*ISNUMBER(D40))+((C41="Tyskland")*ISNUMBER(D41))+((G41="Tyskland")*ISNUMBER(D41))+((C42="Tyskland")*ISNUMBER(D42))+((G42="Tyskland")*ISNUMBER(D42))+((C43="Tyskland")*ISNUMBER(D43))+((G43="Tyskland")*ISNUMBER(D43))+((C44="Tyskland")*ISNUMBER(D44))+((G44="Tyskland")*ISNUMBER(D44))</f>
@@ -4779,39 +4773,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:32" ht="16.5" customHeight="1">
+    <row r="40" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>26</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C40" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="5">
+        <v>2</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D40" s="5">
-        <v>2</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F40" s="5">
-        <v>1</v>
-      </c>
-      <c r="G40" s="8" t="s">
+      <c r="H40" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="I40" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I40" s="7" t="s">
-        <v>97</v>
-      </c>
       <c r="J40" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M40" s="4" t="str">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=2,W39,IF(AF40=2,W40,IF(AF41=2,W41,IF(AF42=2,W42,"")))),"")</f>
@@ -4850,7 +4844,7 @@
         <v>6</v>
       </c>
       <c r="W40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X40">
         <f>((C39="Curaçao")*ISNUMBER(D39))+((G39="Curaçao")*ISNUMBER(D39))+((C40="Curaçao")*ISNUMBER(D40))+((G40="Curaçao")*ISNUMBER(D40))+((C41="Curaçao")*ISNUMBER(D41))+((G41="Curaçao")*ISNUMBER(D41))+((C42="Curaçao")*ISNUMBER(D42))+((G42="Curaçao")*ISNUMBER(D42))+((C43="Curaçao")*ISNUMBER(D43))+((G43="Curaçao")*ISNUMBER(D43))+((C44="Curaçao")*ISNUMBER(D44))+((G44="Curaçao")*ISNUMBER(D44))</f>
@@ -4889,39 +4883,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:32" ht="16.5" customHeight="1">
+    <row r="41" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>27</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="D41" s="5">
         <v>2</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F41" s="5">
         <v>1</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M41" s="4" t="str">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=3,W39,IF(AF40=3,W40,IF(AF41=3,W41,IF(AF42=3,W42,"")))),"")</f>
@@ -4960,7 +4954,7 @@
         <v>3</v>
       </c>
       <c r="W41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X41">
         <f>((C39="Elfenbenskysten")*ISNUMBER(D39))+((G39="Elfenbenskysten")*ISNUMBER(D39))+((C40="Elfenbenskysten")*ISNUMBER(D40))+((G40="Elfenbenskysten")*ISNUMBER(D40))+((C41="Elfenbenskysten")*ISNUMBER(D41))+((G41="Elfenbenskysten")*ISNUMBER(D41))+((C42="Elfenbenskysten")*ISNUMBER(D42))+((G42="Elfenbenskysten")*ISNUMBER(D42))+((C43="Elfenbenskysten")*ISNUMBER(D43))+((G43="Elfenbenskysten")*ISNUMBER(D43))+((C44="Elfenbenskysten")*ISNUMBER(D44))+((G44="Elfenbenskysten")*ISNUMBER(D44))</f>
@@ -4999,39 +4993,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:32" ht="16.5" customHeight="1">
+    <row r="42" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>28</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D42" s="5">
         <v>3</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F42" s="5">
         <v>0</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H42" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I42" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="J42" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="J42" s="8" t="s">
-        <v>101</v>
-      </c>
       <c r="K42" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M42" s="4" t="str">
         <f>IF(AND(ISNUMBER(D39),ISNUMBER(D40),ISNUMBER(D41),ISNUMBER(D42),ISNUMBER(D43),ISNUMBER(D44)),IF(AF39=4,W39,IF(AF40=4,W40,IF(AF41=4,W41,IF(AF42=4,W42,"")))),"")</f>
@@ -5070,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X42">
         <f>((C39="Ecuador")*ISNUMBER(D39))+((G39="Ecuador")*ISNUMBER(D39))+((C40="Ecuador")*ISNUMBER(D40))+((G40="Ecuador")*ISNUMBER(D40))+((C41="Ecuador")*ISNUMBER(D41))+((G41="Ecuador")*ISNUMBER(D41))+((C42="Ecuador")*ISNUMBER(D42))+((G42="Ecuador")*ISNUMBER(D42))+((C43="Ecuador")*ISNUMBER(D43))+((G43="Ecuador")*ISNUMBER(D43))+((C44="Ecuador")*ISNUMBER(D44))+((G44="Ecuador")*ISNUMBER(D44))</f>
@@ -5109,195 +5103,195 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:32" ht="16.5" customHeight="1">
+    <row r="43" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>29</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D43" s="5">
         <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F43" s="5">
         <v>3</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:32" ht="16.5" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>30</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D44" s="5">
         <v>0</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F44" s="5">
         <v>2</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A45" s="56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="55"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="55"/>
+      <c r="M45" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="56"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="56"/>
-      <c r="K45" s="56"/>
-      <c r="M45" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="N45" s="57"/>
-      <c r="O45" s="57"/>
-      <c r="P45" s="57"/>
-      <c r="Q45" s="57"/>
-      <c r="R45" s="57"/>
-      <c r="S45" s="57"/>
-      <c r="T45" s="57"/>
-      <c r="U45" s="57"/>
-    </row>
-    <row r="46" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N45" s="56"/>
+      <c r="O45" s="56"/>
+      <c r="P45" s="56"/>
+      <c r="Q45" s="56"/>
+      <c r="R45" s="56"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="56"/>
+      <c r="U45" s="56"/>
+    </row>
+    <row r="46" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="J46" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="M46" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="P46" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="Q46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q46" s="2" t="s">
+      <c r="R46" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R46" s="2" t="s">
+      <c r="S46" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S46" s="2" t="s">
+      <c r="T46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T46" s="2" t="s">
+      <c r="U46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U46" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="47" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>31</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="D47" s="5">
+        <v>2</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47" s="5">
+        <v>1</v>
+      </c>
+      <c r="G47" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D47" s="5">
-        <v>2</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F47" s="5">
-        <v>1</v>
-      </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J47" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="K47" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M47" s="4" t="str">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=1,W47,IF(AF48=1,W48,IF(AF49=1,W49,IF(AF50=1,W50,"")))),"")</f>
@@ -5336,7 +5330,7 @@
         <v>9</v>
       </c>
       <c r="W47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="X47">
         <f>((C47="Nederland")*ISNUMBER(D47))+((G47="Nederland")*ISNUMBER(D47))+((C48="Nederland")*ISNUMBER(D48))+((G48="Nederland")*ISNUMBER(D48))+((C49="Nederland")*ISNUMBER(D49))+((G49="Nederland")*ISNUMBER(D49))+((C50="Nederland")*ISNUMBER(D50))+((G50="Nederland")*ISNUMBER(D50))+((C51="Nederland")*ISNUMBER(D51))+((G51="Nederland")*ISNUMBER(D51))+((C52="Nederland")*ISNUMBER(D52))+((G52="Nederland")*ISNUMBER(D52))</f>
@@ -5375,39 +5369,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:32" ht="16.5" customHeight="1">
+    <row r="48" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>32</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="5">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48" s="5">
+        <v>1</v>
+      </c>
+      <c r="G48" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="5">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F48" s="5">
-        <v>1</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="H48" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M48" s="4" t="str">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=2,W47,IF(AF48=2,W48,IF(AF49=2,W49,IF(AF50=2,W50,"")))),"")</f>
@@ -5446,7 +5440,7 @@
         <v>2</v>
       </c>
       <c r="W48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="X48">
         <f>((C47="Japan")*ISNUMBER(D47))+((G47="Japan")*ISNUMBER(D47))+((C48="Japan")*ISNUMBER(D48))+((G48="Japan")*ISNUMBER(D48))+((C49="Japan")*ISNUMBER(D49))+((G49="Japan")*ISNUMBER(D49))+((C50="Japan")*ISNUMBER(D50))+((G50="Japan")*ISNUMBER(D50))+((C51="Japan")*ISNUMBER(D51))+((G51="Japan")*ISNUMBER(D51))+((C52="Japan")*ISNUMBER(D52))+((G52="Japan")*ISNUMBER(D52))</f>
@@ -5485,39 +5479,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:32" ht="16.5" customHeight="1">
+    <row r="49" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>33</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="D49" s="5">
         <v>2</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I49" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J49" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="K49" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M49" s="4" t="str">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=3,W47,IF(AF48=3,W48,IF(AF49=3,W49,IF(AF50=3,W50,"")))),"")</f>
@@ -5556,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="W49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X49">
         <f>((C47="Sverige")*ISNUMBER(D47))+((G47="Sverige")*ISNUMBER(D47))+((C48="Sverige")*ISNUMBER(D48))+((G48="Sverige")*ISNUMBER(D48))+((C49="Sverige")*ISNUMBER(D49))+((G49="Sverige")*ISNUMBER(D49))+((C50="Sverige")*ISNUMBER(D50))+((G50="Sverige")*ISNUMBER(D50))+((C51="Sverige")*ISNUMBER(D51))+((G51="Sverige")*ISNUMBER(D51))+((C52="Sverige")*ISNUMBER(D52))+((G52="Sverige")*ISNUMBER(D52))</f>
@@ -5595,39 +5589,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:32" ht="16.5" customHeight="1">
+    <row r="50" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>34</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D50" s="5">
         <v>2</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F50" s="5">
         <v>2</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K50" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M50" s="4" t="str">
         <f>IF(AND(ISNUMBER(D47),ISNUMBER(D48),ISNUMBER(D49),ISNUMBER(D50),ISNUMBER(D51),ISNUMBER(D52)),IF(AF47=4,W47,IF(AF48=4,W48,IF(AF49=4,W49,IF(AF50=4,W50,"")))),"")</f>
@@ -5666,7 +5660,7 @@
         <v>2</v>
       </c>
       <c r="W50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X50">
         <f>((C47="Tunisia")*ISNUMBER(D47))+((G47="Tunisia")*ISNUMBER(D47))+((C48="Tunisia")*ISNUMBER(D48))+((G48="Tunisia")*ISNUMBER(D48))+((C49="Tunisia")*ISNUMBER(D49))+((G49="Tunisia")*ISNUMBER(D49))+((C50="Tunisia")*ISNUMBER(D50))+((G50="Tunisia")*ISNUMBER(D50))+((C51="Tunisia")*ISNUMBER(D51))+((G51="Tunisia")*ISNUMBER(D51))+((C52="Tunisia")*ISNUMBER(D52))+((G52="Tunisia")*ISNUMBER(D52))</f>
@@ -5705,195 +5699,195 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:32" ht="16.5" customHeight="1">
+    <row r="51" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>35</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="5">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="5">
+        <v>2</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D51" s="5">
-        <v>1</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F51" s="5">
-        <v>2</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="H51" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:32" ht="16.5" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>36</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="5">
+        <v>2</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="5">
+        <v>2</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J52" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D52" s="5">
-        <v>2</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F52" s="5">
-        <v>2</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>107</v>
-      </c>
       <c r="K52" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A53" s="56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="55"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="55"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+      <c r="M53" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
-      <c r="M53" s="57" t="s">
-        <v>111</v>
-      </c>
-      <c r="N53" s="57"/>
-      <c r="O53" s="57"/>
-      <c r="P53" s="57"/>
-      <c r="Q53" s="57"/>
-      <c r="R53" s="57"/>
-      <c r="S53" s="57"/>
-      <c r="T53" s="57"/>
-      <c r="U53" s="57"/>
-    </row>
-    <row r="54" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N53" s="56"/>
+      <c r="O53" s="56"/>
+      <c r="P53" s="56"/>
+      <c r="Q53" s="56"/>
+      <c r="R53" s="56"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="56"/>
+      <c r="U53" s="56"/>
+    </row>
+    <row r="54" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="J54" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="K54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="M54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="N54" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N54" s="2" t="s">
+      <c r="O54" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O54" s="2" t="s">
+      <c r="P54" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P54" s="2" t="s">
+      <c r="Q54" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q54" s="2" t="s">
+      <c r="R54" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R54" s="2" t="s">
+      <c r="S54" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S54" s="2" t="s">
+      <c r="T54" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T54" s="2" t="s">
+      <c r="U54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U54" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="55" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>37</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D55" s="5">
+        <v>3</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55" s="5">
+        <v>2</v>
+      </c>
+      <c r="G55" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D55" s="5">
-        <v>3</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F55" s="5">
-        <v>2</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="H55" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K55" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M55" s="4" t="str">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=1,W55,IF(AF56=1,W56,IF(AF57=1,W57,IF(AF58=1,W58,"")))),"")</f>
@@ -5932,7 +5926,7 @@
         <v>9</v>
       </c>
       <c r="W55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="X55">
         <f>((C55="Belgia")*ISNUMBER(D55))+((G55="Belgia")*ISNUMBER(D55))+((C56="Belgia")*ISNUMBER(D56))+((G56="Belgia")*ISNUMBER(D56))+((C57="Belgia")*ISNUMBER(D57))+((G57="Belgia")*ISNUMBER(D57))+((C58="Belgia")*ISNUMBER(D58))+((G58="Belgia")*ISNUMBER(D58))+((C59="Belgia")*ISNUMBER(D59))+((G59="Belgia")*ISNUMBER(D59))+((C60="Belgia")*ISNUMBER(D60))+((G60="Belgia")*ISNUMBER(D60))</f>
@@ -5971,39 +5965,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:32" ht="16.5" customHeight="1">
+    <row r="56" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>38</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C56" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D56" s="5">
+        <v>1</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56" s="5">
+        <v>1</v>
+      </c>
+      <c r="G56" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D56" s="5">
-        <v>1</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F56" s="5">
-        <v>1</v>
-      </c>
-      <c r="G56" s="8" t="s">
+      <c r="H56" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="H56" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="I56" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K56" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M56" s="4" t="str">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=2,W55,IF(AF56=2,W56,IF(AF57=2,W57,IF(AF58=2,W58,"")))),"")</f>
@@ -6042,7 +6036,7 @@
         <v>6</v>
       </c>
       <c r="W56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="X56">
         <f>((C55="Egypt")*ISNUMBER(D55))+((G55="Egypt")*ISNUMBER(D55))+((C56="Egypt")*ISNUMBER(D56))+((G56="Egypt")*ISNUMBER(D56))+((C57="Egypt")*ISNUMBER(D57))+((G57="Egypt")*ISNUMBER(D57))+((C58="Egypt")*ISNUMBER(D58))+((G58="Egypt")*ISNUMBER(D58))+((C59="Egypt")*ISNUMBER(D59))+((G59="Egypt")*ISNUMBER(D59))+((C60="Egypt")*ISNUMBER(D60))+((G60="Egypt")*ISNUMBER(D60))</f>
@@ -6081,39 +6075,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:32" ht="16.5" customHeight="1">
+    <row r="57" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>39</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="D57" s="5">
         <v>2</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F57" s="5">
         <v>0</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M57" s="4" t="str">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=3,W55,IF(AF56=3,W56,IF(AF57=3,W57,IF(AF58=3,W58,"")))),"")</f>
@@ -6152,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="W57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="X57">
         <f>((C55="Iran")*ISNUMBER(D55))+((G55="Iran")*ISNUMBER(D55))+((C56="Iran")*ISNUMBER(D56))+((G56="Iran")*ISNUMBER(D56))+((C57="Iran")*ISNUMBER(D57))+((G57="Iran")*ISNUMBER(D57))+((C58="Iran")*ISNUMBER(D58))+((G58="Iran")*ISNUMBER(D58))+((C59="Iran")*ISNUMBER(D59))+((G59="Iran")*ISNUMBER(D59))+((C60="Iran")*ISNUMBER(D60))+((G60="Iran")*ISNUMBER(D60))</f>
@@ -6191,39 +6185,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:32" ht="16.5" customHeight="1">
+    <row r="58" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>40</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D58" s="5">
         <v>1</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F58" s="5">
         <v>2</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M58" s="4" t="str">
         <f>IF(AND(ISNUMBER(D55),ISNUMBER(D56),ISNUMBER(D57),ISNUMBER(D58),ISNUMBER(D59),ISNUMBER(D60)),IF(AF55=4,W55,IF(AF56=4,W56,IF(AF57=4,W57,IF(AF58=4,W58,"")))),"")</f>
@@ -6262,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="W58" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="X58">
         <f>((C55="New Zealand")*ISNUMBER(D55))+((G55="New Zealand")*ISNUMBER(D55))+((C56="New Zealand")*ISNUMBER(D56))+((G56="New Zealand")*ISNUMBER(D56))+((C57="New Zealand")*ISNUMBER(D57))+((G57="New Zealand")*ISNUMBER(D57))+((C58="New Zealand")*ISNUMBER(D58))+((G58="New Zealand")*ISNUMBER(D58))+((C59="New Zealand")*ISNUMBER(D59))+((G59="New Zealand")*ISNUMBER(D59))+((C60="New Zealand")*ISNUMBER(D60))+((G60="New Zealand")*ISNUMBER(D60))</f>
@@ -6301,195 +6295,195 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:32" ht="16.5" customHeight="1">
+    <row r="59" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>41</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D59" s="5">
         <v>2</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F59" s="5">
         <v>0</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H59" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="J59" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:32" ht="16.5" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>42</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D60" s="5">
         <v>0</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F60" s="5">
         <v>3</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H60" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="J60" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="J60" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A61" s="56" t="s">
+      <c r="B61" s="55"/>
+      <c r="C61" s="55"/>
+      <c r="D61" s="55"/>
+      <c r="E61" s="55"/>
+      <c r="F61" s="55"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="55"/>
+      <c r="I61" s="55"/>
+      <c r="J61" s="55"/>
+      <c r="K61" s="55"/>
+      <c r="M61" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="B61" s="56"/>
-      <c r="C61" s="56"/>
-      <c r="D61" s="56"/>
-      <c r="E61" s="56"/>
-      <c r="F61" s="56"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="56"/>
-      <c r="J61" s="56"/>
-      <c r="K61" s="56"/>
-      <c r="M61" s="57" t="s">
-        <v>122</v>
-      </c>
-      <c r="N61" s="57"/>
-      <c r="O61" s="57"/>
-      <c r="P61" s="57"/>
-      <c r="Q61" s="57"/>
-      <c r="R61" s="57"/>
-      <c r="S61" s="57"/>
-      <c r="T61" s="57"/>
-      <c r="U61" s="57"/>
-    </row>
-    <row r="62" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N61" s="56"/>
+      <c r="O61" s="56"/>
+      <c r="P61" s="56"/>
+      <c r="Q61" s="56"/>
+      <c r="R61" s="56"/>
+      <c r="S61" s="56"/>
+      <c r="T61" s="56"/>
+      <c r="U61" s="56"/>
+    </row>
+    <row r="62" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="D62" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="H62" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="I62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="J62" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J62" s="1" t="s">
+      <c r="K62" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="M62" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="N62" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N62" s="2" t="s">
+      <c r="O62" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O62" s="2" t="s">
+      <c r="P62" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P62" s="2" t="s">
+      <c r="Q62" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q62" s="2" t="s">
+      <c r="R62" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R62" s="2" t="s">
+      <c r="S62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S62" s="2" t="s">
+      <c r="T62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T62" s="2" t="s">
+      <c r="U62" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U62" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="63" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>43</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="D63" s="5">
         <v>3</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J63" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J63" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="K63" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M63" s="4" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=1,W63,IF(AF64=1,W64,IF(AF65=1,W65,IF(AF66=1,W66,"")))),"")</f>
@@ -6528,7 +6522,7 @@
         <v>9</v>
       </c>
       <c r="W63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X63">
         <f>((C63="Spania")*ISNUMBER(D63))+((G63="Spania")*ISNUMBER(D63))+((C64="Spania")*ISNUMBER(D64))+((G64="Spania")*ISNUMBER(D64))+((C65="Spania")*ISNUMBER(D65))+((G65="Spania")*ISNUMBER(D65))+((C66="Spania")*ISNUMBER(D66))+((G66="Spania")*ISNUMBER(D66))+((C67="Spania")*ISNUMBER(D67))+((G67="Spania")*ISNUMBER(D67))+((C68="Spania")*ISNUMBER(D68))+((G68="Spania")*ISNUMBER(D68))</f>
@@ -6567,39 +6561,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:32" ht="16.5" customHeight="1">
+    <row r="64" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>44</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D64" s="5">
         <v>0</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F64" s="5">
         <v>2</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K64" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M64" s="4" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=2,W63,IF(AF64=2,W64,IF(AF65=2,W65,IF(AF66=2,W66,"")))),"")</f>
@@ -6638,7 +6632,7 @@
         <v>6</v>
       </c>
       <c r="W64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X64">
         <f>((C63="Kapp Verde")*ISNUMBER(D63))+((G63="Kapp Verde")*ISNUMBER(D63))+((C64="Kapp Verde")*ISNUMBER(D64))+((G64="Kapp Verde")*ISNUMBER(D64))+((C65="Kapp Verde")*ISNUMBER(D65))+((G65="Kapp Verde")*ISNUMBER(D65))+((C66="Kapp Verde")*ISNUMBER(D66))+((G66="Kapp Verde")*ISNUMBER(D66))+((C67="Kapp Verde")*ISNUMBER(D67))+((G67="Kapp Verde")*ISNUMBER(D67))+((C68="Kapp Verde")*ISNUMBER(D68))+((G68="Kapp Verde")*ISNUMBER(D68))</f>
@@ -6677,39 +6671,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:32" ht="16.5" customHeight="1">
+    <row r="65" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>45</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="D65" s="5">
         <v>3</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F65" s="5">
         <v>1</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I65" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J65" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J65" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="K65" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M65" s="4" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=3,W63,IF(AF64=3,W64,IF(AF65=3,W65,IF(AF66=3,W66,"")))),"")</f>
@@ -6748,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="W65" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X65">
         <f>((C63="Saudi Arabia")*ISNUMBER(D63))+((G63="Saudi Arabia")*ISNUMBER(D63))+((C64="Saudi Arabia")*ISNUMBER(D64))+((G64="Saudi Arabia")*ISNUMBER(D64))+((C65="Saudi Arabia")*ISNUMBER(D65))+((G65="Saudi Arabia")*ISNUMBER(D65))+((C66="Saudi Arabia")*ISNUMBER(D66))+((G66="Saudi Arabia")*ISNUMBER(D66))+((C67="Saudi Arabia")*ISNUMBER(D67))+((G67="Saudi Arabia")*ISNUMBER(D67))+((C68="Saudi Arabia")*ISNUMBER(D68))+((G68="Saudi Arabia")*ISNUMBER(D68))</f>
@@ -6787,39 +6781,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:32" ht="16.5" customHeight="1">
+    <row r="66" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>46</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D66" s="5">
         <v>3</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F66" s="5">
         <v>1</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J66" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M66" s="4" t="str">
         <f>IF(AND(ISNUMBER(D63),ISNUMBER(D64),ISNUMBER(D65),ISNUMBER(D66),ISNUMBER(D67),ISNUMBER(D68)),IF(AF63=4,W63,IF(AF64=4,W64,IF(AF65=4,W65,IF(AF66=4,W66,"")))),"")</f>
@@ -6858,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="W66" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="X66">
         <f>((C63="Uruguay")*ISNUMBER(D63))+((G63="Uruguay")*ISNUMBER(D63))+((C64="Uruguay")*ISNUMBER(D64))+((G64="Uruguay")*ISNUMBER(D64))+((C65="Uruguay")*ISNUMBER(D65))+((G65="Uruguay")*ISNUMBER(D65))+((C66="Uruguay")*ISNUMBER(D66))+((G66="Uruguay")*ISNUMBER(D66))+((C67="Uruguay")*ISNUMBER(D67))+((G67="Uruguay")*ISNUMBER(D67))+((C68="Uruguay")*ISNUMBER(D68))+((G68="Uruguay")*ISNUMBER(D68))</f>
@@ -6897,195 +6891,195 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:32" ht="16.5" customHeight="1">
+    <row r="67" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>47</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C67" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D67" s="5">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" s="5">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D67" s="5">
-        <v>1</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F67" s="5">
-        <v>1</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="H67" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K67" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="68" spans="1:32" ht="16.5" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>48</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D68" s="5">
         <v>0</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F68" s="5">
         <v>3</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J68" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K68" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K68" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="69" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A69" s="61" t="s">
+    </row>
+    <row r="69" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="60"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="60"/>
+      <c r="J69" s="60"/>
+      <c r="K69" s="60"/>
+      <c r="M69" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="61"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="61"/>
-      <c r="J69" s="61"/>
-      <c r="K69" s="61"/>
-      <c r="M69" s="62" t="s">
-        <v>129</v>
-      </c>
-      <c r="N69" s="62"/>
-      <c r="O69" s="62"/>
-      <c r="P69" s="62"/>
-      <c r="Q69" s="62"/>
-      <c r="R69" s="62"/>
-      <c r="S69" s="62"/>
-      <c r="T69" s="62"/>
-      <c r="U69" s="62"/>
-    </row>
-    <row r="70" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N69" s="61"/>
+      <c r="O69" s="61"/>
+      <c r="P69" s="61"/>
+      <c r="Q69" s="61"/>
+      <c r="R69" s="61"/>
+      <c r="S69" s="61"/>
+      <c r="T69" s="61"/>
+      <c r="U69" s="61"/>
+    </row>
+    <row r="70" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="D70" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="I70" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="M70" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="N70" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N70" s="2" t="s">
+      <c r="O70" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O70" s="2" t="s">
+      <c r="P70" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P70" s="2" t="s">
+      <c r="Q70" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q70" s="2" t="s">
+      <c r="R70" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R70" s="2" t="s">
+      <c r="S70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S70" s="2" t="s">
+      <c r="T70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T70" s="2" t="s">
+      <c r="U70" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U70" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="71" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>49</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="D71" s="5">
+        <v>3</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" s="5">
+        <v>1</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D71" s="5">
-        <v>3</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F71" s="5">
-        <v>1</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="H71" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M71" s="4" t="str">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=1,W71,IF(AF72=1,W72,IF(AF73=1,W73,IF(AF74=1,W74,"")))),"")</f>
@@ -7124,7 +7118,7 @@
         <v>7</v>
       </c>
       <c r="W71" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="X71">
         <f>((C71="Frankrike")*ISNUMBER(D71))+((G71="Frankrike")*ISNUMBER(D71))+((C72="Frankrike")*ISNUMBER(D72))+((G72="Frankrike")*ISNUMBER(D72))+((C73="Frankrike")*ISNUMBER(D73))+((G73="Frankrike")*ISNUMBER(D73))+((C74="Frankrike")*ISNUMBER(D74))+((G74="Frankrike")*ISNUMBER(D74))+((C75="Frankrike")*ISNUMBER(D75))+((G75="Frankrike")*ISNUMBER(D75))+((C76="Frankrike")*ISNUMBER(D76))+((G76="Frankrike")*ISNUMBER(D76))</f>
@@ -7163,39 +7157,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:32" ht="16.5" customHeight="1">
+    <row r="72" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>50</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C72" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D72" s="5">
+        <v>1</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72" s="5">
+        <v>3</v>
+      </c>
+      <c r="G72" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D72" s="5">
-        <v>1</v>
-      </c>
-      <c r="E72" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F72" s="5">
-        <v>3</v>
-      </c>
-      <c r="G72" s="11" t="s">
+      <c r="H72" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="H72" s="10" t="s">
-        <v>135</v>
-      </c>
       <c r="I72" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M72" s="4" t="str">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=2,W71,IF(AF72=2,W72,IF(AF73=2,W73,IF(AF74=2,W74,"")))),"")</f>
@@ -7234,7 +7228,7 @@
         <v>6</v>
       </c>
       <c r="W72" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="X72">
         <f>((C71="Senegal")*ISNUMBER(D71))+((G71="Senegal")*ISNUMBER(D71))+((C72="Senegal")*ISNUMBER(D72))+((G72="Senegal")*ISNUMBER(D72))+((C73="Senegal")*ISNUMBER(D73))+((G73="Senegal")*ISNUMBER(D73))+((C74="Senegal")*ISNUMBER(D74))+((G74="Senegal")*ISNUMBER(D74))+((C75="Senegal")*ISNUMBER(D75))+((G75="Senegal")*ISNUMBER(D75))+((C76="Senegal")*ISNUMBER(D76))+((G76="Senegal")*ISNUMBER(D76))</f>
@@ -7273,39 +7267,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:32" ht="16.5" customHeight="1">
+    <row r="73" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>51</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="D73" s="5">
         <v>3</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F73" s="5">
         <v>0</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K73" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M73" s="4" t="str">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=3,W71,IF(AF72=3,W72,IF(AF73=3,W73,IF(AF74=3,W74,"")))),"")</f>
@@ -7344,7 +7338,7 @@
         <v>4</v>
       </c>
       <c r="W73" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="X73">
         <f>((C71="Irak")*ISNUMBER(D71))+((G71="Irak")*ISNUMBER(D71))+((C72="Irak")*ISNUMBER(D72))+((G72="Irak")*ISNUMBER(D72))+((C73="Irak")*ISNUMBER(D73))+((G73="Irak")*ISNUMBER(D73))+((C74="Irak")*ISNUMBER(D74))+((G74="Irak")*ISNUMBER(D74))+((C75="Irak")*ISNUMBER(D75))+((G75="Irak")*ISNUMBER(D75))+((C76="Irak")*ISNUMBER(D76))+((G76="Irak")*ISNUMBER(D76))</f>
@@ -7383,39 +7377,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:32" ht="16.5" customHeight="1">
+    <row r="74" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>52</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D74" s="5">
         <v>2</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F74" s="5">
         <v>3</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K74" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M74" s="4" t="str">
         <f>IF(AND(ISNUMBER(D71),ISNUMBER(D72),ISNUMBER(D73),ISNUMBER(D74),ISNUMBER(D75),ISNUMBER(D76)),IF(AF71=4,W71,IF(AF72=4,W72,IF(AF73=4,W73,IF(AF74=4,W74,"")))),"")</f>
@@ -7454,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="W74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="X74">
         <f>((C71="Norge")*ISNUMBER(D71))+((G71="Norge")*ISNUMBER(D71))+((C72="Norge")*ISNUMBER(D72))+((G72="Norge")*ISNUMBER(D72))+((C73="Norge")*ISNUMBER(D73))+((G73="Norge")*ISNUMBER(D73))+((C74="Norge")*ISNUMBER(D74))+((G74="Norge")*ISNUMBER(D74))+((C75="Norge")*ISNUMBER(D75))+((G75="Norge")*ISNUMBER(D75))+((C76="Norge")*ISNUMBER(D76))+((G76="Norge")*ISNUMBER(D76))</f>
@@ -7493,195 +7487,195 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:32" ht="16.5" customHeight="1">
+    <row r="75" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>53</v>
       </c>
       <c r="B75" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="D75" s="5">
+        <v>2</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" s="5">
+        <v>2</v>
+      </c>
+      <c r="G75" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C75" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D75" s="5">
-        <v>2</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F75" s="5">
-        <v>2</v>
-      </c>
-      <c r="G75" s="11" t="s">
-        <v>131</v>
-      </c>
       <c r="H75" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K75" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="76" spans="1:32" ht="16.5" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>54</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D76" s="5">
         <v>1</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F76" s="5">
         <v>0</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J76" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K76" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="77" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A77" s="56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="B77" s="55"/>
+      <c r="C77" s="55"/>
+      <c r="D77" s="55"/>
+      <c r="E77" s="55"/>
+      <c r="F77" s="55"/>
+      <c r="G77" s="55"/>
+      <c r="H77" s="55"/>
+      <c r="I77" s="55"/>
+      <c r="J77" s="55"/>
+      <c r="K77" s="55"/>
+      <c r="M77" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="B77" s="56"/>
-      <c r="C77" s="56"/>
-      <c r="D77" s="56"/>
-      <c r="E77" s="56"/>
-      <c r="F77" s="56"/>
-      <c r="G77" s="56"/>
-      <c r="H77" s="56"/>
-      <c r="I77" s="56"/>
-      <c r="J77" s="56"/>
-      <c r="K77" s="56"/>
-      <c r="M77" s="57" t="s">
-        <v>139</v>
-      </c>
-      <c r="N77" s="57"/>
-      <c r="O77" s="57"/>
-      <c r="P77" s="57"/>
-      <c r="Q77" s="57"/>
-      <c r="R77" s="57"/>
-      <c r="S77" s="57"/>
-      <c r="T77" s="57"/>
-      <c r="U77" s="57"/>
-    </row>
-    <row r="78" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N77" s="56"/>
+      <c r="O77" s="56"/>
+      <c r="P77" s="56"/>
+      <c r="Q77" s="56"/>
+      <c r="R77" s="56"/>
+      <c r="S77" s="56"/>
+      <c r="T77" s="56"/>
+      <c r="U77" s="56"/>
+    </row>
+    <row r="78" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="J78" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J78" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K78" s="1" t="s">
+      <c r="M78" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M78" s="2" t="s">
+      <c r="N78" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N78" s="2" t="s">
+      <c r="O78" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O78" s="2" t="s">
+      <c r="P78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P78" s="2" t="s">
+      <c r="Q78" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q78" s="2" t="s">
+      <c r="R78" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R78" s="2" t="s">
+      <c r="S78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S78" s="2" t="s">
+      <c r="T78" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T78" s="2" t="s">
+      <c r="U78" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U78" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="79" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>55</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="D79" s="5">
+        <v>2</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79" s="5">
+        <v>1</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="5">
-        <v>2</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F79" s="5">
-        <v>1</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="H79" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K79" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M79" s="4" t="str">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=1,W79,IF(AF80=1,W80,IF(AF81=1,W81,IF(AF82=1,W82,"")))),"")</f>
@@ -7720,7 +7714,7 @@
         <v>9</v>
       </c>
       <c r="W79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="X79">
         <f>((C79="Argentina")*ISNUMBER(D79))+((G79="Argentina")*ISNUMBER(D79))+((C80="Argentina")*ISNUMBER(D80))+((G80="Argentina")*ISNUMBER(D80))+((C81="Argentina")*ISNUMBER(D81))+((G81="Argentina")*ISNUMBER(D81))+((C82="Argentina")*ISNUMBER(D82))+((G82="Argentina")*ISNUMBER(D82))+((C83="Argentina")*ISNUMBER(D83))+((G83="Argentina")*ISNUMBER(D83))+((C84="Argentina")*ISNUMBER(D84))+((G84="Argentina")*ISNUMBER(D84))</f>
@@ -7759,39 +7753,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:32" ht="16.5" customHeight="1">
+    <row r="80" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>56</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D80" s="5">
         <v>4</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F80" s="5">
         <v>0</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J80" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K80" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M80" s="4" t="str">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=2,W79,IF(AF80=2,W80,IF(AF81=2,W81,IF(AF82=2,W82,"")))),"")</f>
@@ -7830,7 +7824,7 @@
         <v>6</v>
       </c>
       <c r="W80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="X80">
         <f>((C79="Algerie")*ISNUMBER(D79))+((G79="Algerie")*ISNUMBER(D79))+((C80="Algerie")*ISNUMBER(D80))+((G80="Algerie")*ISNUMBER(D80))+((C81="Algerie")*ISNUMBER(D81))+((G81="Algerie")*ISNUMBER(D81))+((C82="Algerie")*ISNUMBER(D82))+((G82="Algerie")*ISNUMBER(D82))+((C83="Algerie")*ISNUMBER(D83))+((G83="Algerie")*ISNUMBER(D83))+((C84="Algerie")*ISNUMBER(D84))+((G84="Algerie")*ISNUMBER(D84))</f>
@@ -7869,39 +7863,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:32" ht="16.5" customHeight="1">
+    <row r="81" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>57</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="D81" s="5">
         <v>1</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F81" s="5">
         <v>0</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M81" s="4" t="str">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=3,W79,IF(AF80=3,W80,IF(AF81=3,W81,IF(AF82=3,W82,"")))),"")</f>
@@ -7940,7 +7934,7 @@
         <v>3</v>
       </c>
       <c r="W81" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="X81">
         <f>((C79="Østerrike")*ISNUMBER(D79))+((G79="Østerrike")*ISNUMBER(D79))+((C80="Østerrike")*ISNUMBER(D80))+((G80="Østerrike")*ISNUMBER(D80))+((C81="Østerrike")*ISNUMBER(D81))+((G81="Østerrike")*ISNUMBER(D81))+((C82="Østerrike")*ISNUMBER(D82))+((G82="Østerrike")*ISNUMBER(D82))+((C83="Østerrike")*ISNUMBER(D83))+((G83="Østerrike")*ISNUMBER(D83))+((C84="Østerrike")*ISNUMBER(D84))+((G84="Østerrike")*ISNUMBER(D84))</f>
@@ -7979,39 +7973,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:32" ht="16.5" customHeight="1">
+    <row r="82" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>58</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D82" s="5">
         <v>0</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F82" s="5">
         <v>1</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J82" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M82" s="4" t="str">
         <f>IF(AND(ISNUMBER(D79),ISNUMBER(D80),ISNUMBER(D81),ISNUMBER(D82),ISNUMBER(D83),ISNUMBER(D84)),IF(AF79=4,W79,IF(AF80=4,W80,IF(AF81=4,W81,IF(AF82=4,W82,"")))),"")</f>
@@ -8050,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="W82" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X82">
         <f>((C79="Jordan")*ISNUMBER(D79))+((G79="Jordan")*ISNUMBER(D79))+((C80="Jordan")*ISNUMBER(D80))+((G80="Jordan")*ISNUMBER(D80))+((C81="Jordan")*ISNUMBER(D81))+((G81="Jordan")*ISNUMBER(D81))+((C82="Jordan")*ISNUMBER(D82))+((G82="Jordan")*ISNUMBER(D82))+((C83="Jordan")*ISNUMBER(D83))+((G83="Jordan")*ISNUMBER(D83))+((C84="Jordan")*ISNUMBER(D84))+((G84="Jordan")*ISNUMBER(D84))</f>
@@ -8089,195 +8083,195 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:32" ht="16.5" customHeight="1">
+    <row r="83" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>59</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D83" s="5">
         <v>0</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F83" s="5">
         <v>2</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K83" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="84" spans="1:32" ht="16.5" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>60</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D84" s="5">
         <v>0</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F84" s="5">
         <v>1</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K84" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="85" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A85" s="56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="85" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="55" t="s">
+        <v>144</v>
+      </c>
+      <c r="B85" s="55"/>
+      <c r="C85" s="55"/>
+      <c r="D85" s="55"/>
+      <c r="E85" s="55"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="55"/>
+      <c r="H85" s="55"/>
+      <c r="I85" s="55"/>
+      <c r="J85" s="55"/>
+      <c r="K85" s="55"/>
+      <c r="M85" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="B85" s="56"/>
-      <c r="C85" s="56"/>
-      <c r="D85" s="56"/>
-      <c r="E85" s="56"/>
-      <c r="F85" s="56"/>
-      <c r="G85" s="56"/>
-      <c r="H85" s="56"/>
-      <c r="I85" s="56"/>
-      <c r="J85" s="56"/>
-      <c r="K85" s="56"/>
-      <c r="M85" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="N85" s="57"/>
-      <c r="O85" s="57"/>
-      <c r="P85" s="57"/>
-      <c r="Q85" s="57"/>
-      <c r="R85" s="57"/>
-      <c r="S85" s="57"/>
-      <c r="T85" s="57"/>
-      <c r="U85" s="57"/>
-    </row>
-    <row r="86" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N85" s="56"/>
+      <c r="O85" s="56"/>
+      <c r="P85" s="56"/>
+      <c r="Q85" s="56"/>
+      <c r="R85" s="56"/>
+      <c r="S85" s="56"/>
+      <c r="T85" s="56"/>
+      <c r="U85" s="56"/>
+    </row>
+    <row r="86" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="D86" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="H86" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="I86" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I86" s="1" t="s">
+      <c r="J86" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J86" s="1" t="s">
+      <c r="K86" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="M86" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="N86" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N86" s="2" t="s">
+      <c r="O86" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O86" s="2" t="s">
+      <c r="P86" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P86" s="2" t="s">
+      <c r="Q86" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q86" s="2" t="s">
+      <c r="R86" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R86" s="2" t="s">
+      <c r="S86" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S86" s="2" t="s">
+      <c r="T86" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T86" s="2" t="s">
+      <c r="U86" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U86" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="87" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>61</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="D87" s="5">
+        <v>2</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87" s="5">
+        <v>1</v>
+      </c>
+      <c r="G87" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D87" s="5">
-        <v>2</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F87" s="5">
-        <v>1</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="H87" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I87" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J87" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J87" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="K87" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M87" s="4" t="str">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=1,W87,IF(AF88=1,W88,IF(AF89=1,W89,IF(AF90=1,W90,"")))),"")</f>
@@ -8316,7 +8310,7 @@
         <v>9</v>
       </c>
       <c r="W87" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="X87">
         <f>((C87="Portugal")*ISNUMBER(D87))+((G87="Portugal")*ISNUMBER(D87))+((C88="Portugal")*ISNUMBER(D88))+((G88="Portugal")*ISNUMBER(D88))+((C89="Portugal")*ISNUMBER(D89))+((G89="Portugal")*ISNUMBER(D89))+((C90="Portugal")*ISNUMBER(D90))+((G90="Portugal")*ISNUMBER(D90))+((C91="Portugal")*ISNUMBER(D91))+((G91="Portugal")*ISNUMBER(D91))+((C92="Portugal")*ISNUMBER(D92))+((G92="Portugal")*ISNUMBER(D92))</f>
@@ -8355,39 +8349,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:32" ht="16.5" customHeight="1">
+    <row r="88" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>62</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D88" s="5">
         <v>0</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F88" s="5">
         <v>2</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J88" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K88" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="M88" s="4" t="str">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=2,W87,IF(AF88=2,W88,IF(AF89=2,W89,IF(AF90=2,W90,"")))),"")</f>
@@ -8426,7 +8420,7 @@
         <v>4</v>
       </c>
       <c r="W88" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="X88">
         <f>((C87="DR Kongo")*ISNUMBER(D87))+((G87="DR Kongo")*ISNUMBER(D87))+((C88="DR Kongo")*ISNUMBER(D88))+((G88="DR Kongo")*ISNUMBER(D88))+((C89="DR Kongo")*ISNUMBER(D89))+((G89="DR Kongo")*ISNUMBER(D89))+((C90="DR Kongo")*ISNUMBER(D90))+((G90="DR Kongo")*ISNUMBER(D90))+((C91="DR Kongo")*ISNUMBER(D91))+((G91="DR Kongo")*ISNUMBER(D91))+((C92="DR Kongo")*ISNUMBER(D92))+((G92="DR Kongo")*ISNUMBER(D92))</f>
@@ -8465,39 +8459,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:32" ht="16.5" customHeight="1">
+    <row r="89" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>63</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>148</v>
-      </c>
       <c r="D89" s="5">
         <v>2</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F89" s="5">
         <v>0</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I89" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J89" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J89" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="K89" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M89" s="4" t="str">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=3,W87,IF(AF88=3,W88,IF(AF89=3,W89,IF(AF90=3,W90,"")))),"")</f>
@@ -8536,7 +8530,7 @@
         <v>4</v>
       </c>
       <c r="W89" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="X89">
         <f>((C87="Usbekistan")*ISNUMBER(D87))+((G87="Usbekistan")*ISNUMBER(D87))+((C88="Usbekistan")*ISNUMBER(D88))+((G88="Usbekistan")*ISNUMBER(D88))+((C89="Usbekistan")*ISNUMBER(D89))+((G89="Usbekistan")*ISNUMBER(D89))+((C90="Usbekistan")*ISNUMBER(D90))+((G90="Usbekistan")*ISNUMBER(D90))+((C91="Usbekistan")*ISNUMBER(D91))+((G91="Usbekistan")*ISNUMBER(D91))+((C92="Usbekistan")*ISNUMBER(D92))+((G92="Usbekistan")*ISNUMBER(D92))</f>
@@ -8575,39 +8569,39 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:32" ht="16.5" customHeight="1">
+    <row r="90" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>64</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D90" s="5">
         <v>2</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F90" s="5">
         <v>2</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I90" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J90" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J90" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="K90" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M90" s="4" t="str">
         <f>IF(AND(ISNUMBER(D87),ISNUMBER(D88),ISNUMBER(D89),ISNUMBER(D90),ISNUMBER(D91),ISNUMBER(D92)),IF(AF87=4,W87,IF(AF88=4,W88,IF(AF89=4,W89,IF(AF90=4,W90,"")))),"")</f>
@@ -8646,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="W90" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="X90">
         <f>((C87="Colombia")*ISNUMBER(D87))+((G87="Colombia")*ISNUMBER(D87))+((C88="Colombia")*ISNUMBER(D88))+((G88="Colombia")*ISNUMBER(D88))+((C89="Colombia")*ISNUMBER(D89))+((G89="Colombia")*ISNUMBER(D89))+((C90="Colombia")*ISNUMBER(D90))+((G90="Colombia")*ISNUMBER(D90))+((C91="Colombia")*ISNUMBER(D91))+((G91="Colombia")*ISNUMBER(D91))+((C92="Colombia")*ISNUMBER(D92))+((G92="Colombia")*ISNUMBER(D92))</f>
@@ -8685,195 +8679,195 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" spans="1:32" ht="16.5" customHeight="1">
+    <row r="91" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>65</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D91" s="5">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91" s="5">
+        <v>3</v>
+      </c>
+      <c r="G91" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="H91" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I91" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D91" s="5">
-        <v>1</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F91" s="5">
-        <v>3</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="J91" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K91" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="92" spans="1:32" ht="16.5" customHeight="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>66</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C92" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D92" s="5">
+        <v>3</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92" s="5">
+        <v>1</v>
+      </c>
+      <c r="G92" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D92" s="5">
-        <v>3</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F92" s="5">
-        <v>1</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="H92" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I92" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K92" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="J92" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K92" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="93" spans="1:32" ht="18.75" customHeight="1">
-      <c r="A93" s="56" t="s">
+      <c r="B93" s="55"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="55"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="55"/>
+      <c r="M93" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="B93" s="56"/>
-      <c r="C93" s="56"/>
-      <c r="D93" s="56"/>
-      <c r="E93" s="56"/>
-      <c r="F93" s="56"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="56"/>
-      <c r="I93" s="56"/>
-      <c r="J93" s="56"/>
-      <c r="K93" s="56"/>
-      <c r="M93" s="57" t="s">
-        <v>154</v>
-      </c>
-      <c r="N93" s="57"/>
-      <c r="O93" s="57"/>
-      <c r="P93" s="57"/>
-      <c r="Q93" s="57"/>
-      <c r="R93" s="57"/>
-      <c r="S93" s="57"/>
-      <c r="T93" s="57"/>
-      <c r="U93" s="57"/>
-    </row>
-    <row r="94" spans="1:32" ht="15.75" customHeight="1">
+      <c r="N93" s="56"/>
+      <c r="O93" s="56"/>
+      <c r="P93" s="56"/>
+      <c r="Q93" s="56"/>
+      <c r="R93" s="56"/>
+      <c r="S93" s="56"/>
+      <c r="T93" s="56"/>
+      <c r="U93" s="56"/>
+    </row>
+    <row r="94" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="D94" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="H94" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="I94" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I94" s="1" t="s">
+      <c r="J94" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J94" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="M94" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M94" s="2" t="s">
+      <c r="N94" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N94" s="2" t="s">
+      <c r="O94" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="O94" s="2" t="s">
+      <c r="P94" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P94" s="2" t="s">
+      <c r="Q94" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q94" s="2" t="s">
+      <c r="R94" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="R94" s="2" t="s">
+      <c r="S94" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S94" s="2" t="s">
+      <c r="T94" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="T94" s="2" t="s">
+      <c r="U94" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="U94" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="95" spans="1:32" ht="16.5" customHeight="1">
+    </row>
+    <row r="95" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>67</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="D95" s="5">
+        <v>2</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95" s="5">
+        <v>2</v>
+      </c>
+      <c r="G95" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D95" s="5">
-        <v>2</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F95" s="5">
-        <v>2</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="H95" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K95" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M95" s="4" t="str">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=1,W95,IF(AF96=1,W96,IF(AF97=1,W97,IF(AF98=1,W98,"")))),"")</f>
@@ -8912,7 +8906,7 @@
         <v>7</v>
       </c>
       <c r="W95" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X95">
         <f>((C95="England")*ISNUMBER(D95))+((G95="England")*ISNUMBER(D95))+((C96="England")*ISNUMBER(D96))+((G96="England")*ISNUMBER(D96))+((C97="England")*ISNUMBER(D97))+((G97="England")*ISNUMBER(D97))+((C98="England")*ISNUMBER(D98))+((G98="England")*ISNUMBER(D98))+((C99="England")*ISNUMBER(D99))+((G99="England")*ISNUMBER(D99))+((C100="England")*ISNUMBER(D100))+((G100="England")*ISNUMBER(D100))</f>
@@ -8951,39 +8945,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:32" ht="16.5" customHeight="1">
+    <row r="96" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>68</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C96" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D96" s="5">
+        <v>2</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F96" s="5">
+        <v>2</v>
+      </c>
+      <c r="G96" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="D96" s="5">
-        <v>2</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F96" s="5">
-        <v>2</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>159</v>
-      </c>
       <c r="H96" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J96" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M96" s="4" t="str">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=2,W95,IF(AF96=2,W96,IF(AF97=2,W97,IF(AF98=2,W98,"")))),"")</f>
@@ -9022,7 +9016,7 @@
         <v>5</v>
       </c>
       <c r="W96" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="X96">
         <f>((C95="Kroatia")*ISNUMBER(D95))+((G95="Kroatia")*ISNUMBER(D95))+((C96="Kroatia")*ISNUMBER(D96))+((G96="Kroatia")*ISNUMBER(D96))+((C97="Kroatia")*ISNUMBER(D97))+((G97="Kroatia")*ISNUMBER(D97))+((C98="Kroatia")*ISNUMBER(D98))+((G98="Kroatia")*ISNUMBER(D98))+((C99="Kroatia")*ISNUMBER(D99))+((G99="Kroatia")*ISNUMBER(D99))+((C100="Kroatia")*ISNUMBER(D100))+((G100="Kroatia")*ISNUMBER(D100))</f>
@@ -9061,39 +9055,39 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:32" ht="16.5" customHeight="1">
+    <row r="97" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>69</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="D97" s="5">
         <v>2</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F97" s="5">
         <v>0</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K97" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M97" s="4" t="str">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=3,W95,IF(AF96=3,W96,IF(AF97=3,W97,IF(AF98=3,W98,"")))),"")</f>
@@ -9132,7 +9126,7 @@
         <v>2</v>
       </c>
       <c r="W97" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="X97">
         <f>((C95="Ghana")*ISNUMBER(D95))+((G95="Ghana")*ISNUMBER(D95))+((C96="Ghana")*ISNUMBER(D96))+((G96="Ghana")*ISNUMBER(D96))+((C97="Ghana")*ISNUMBER(D97))+((G97="Ghana")*ISNUMBER(D97))+((C98="Ghana")*ISNUMBER(D98))+((G98="Ghana")*ISNUMBER(D98))+((C99="Ghana")*ISNUMBER(D99))+((G99="Ghana")*ISNUMBER(D99))+((C100="Ghana")*ISNUMBER(D100))+((G100="Ghana")*ISNUMBER(D100))</f>
@@ -9171,39 +9165,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:32" ht="16.5" customHeight="1">
+    <row r="98" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>70</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D98" s="5">
         <v>0</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F98" s="5">
         <v>3</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J98" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K98" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M98" s="4" t="str">
         <f>IF(AND(ISNUMBER(D95),ISNUMBER(D96),ISNUMBER(D97),ISNUMBER(D98),ISNUMBER(D99),ISNUMBER(D100)),IF(AF95=4,W95,IF(AF96=4,W96,IF(AF97=4,W97,IF(AF98=4,W98,"")))),"")</f>
@@ -9242,7 +9236,7 @@
         <v>1</v>
       </c>
       <c r="W98" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="X98">
         <f>((C95="Panama")*ISNUMBER(D95))+((G95="Panama")*ISNUMBER(D95))+((C96="Panama")*ISNUMBER(D96))+((G96="Panama")*ISNUMBER(D96))+((C97="Panama")*ISNUMBER(D97))+((G97="Panama")*ISNUMBER(D97))+((C98="Panama")*ISNUMBER(D98))+((G98="Panama")*ISNUMBER(D98))+((C99="Panama")*ISNUMBER(D99))+((G99="Panama")*ISNUMBER(D99))+((C100="Panama")*ISNUMBER(D100))+((G100="Panama")*ISNUMBER(D100))</f>
@@ -9281,77 +9275,77 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:32" ht="16.5" customHeight="1">
+    <row r="99" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>71</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99" s="5">
+        <v>1</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99" s="5">
+        <v>3</v>
+      </c>
+      <c r="G99" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D99" s="5">
-        <v>1</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F99" s="5">
-        <v>3</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="H99" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="100" spans="1:32" ht="16.5" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100" spans="1:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>72</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C100" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D100" s="5">
+        <v>2</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100" s="5">
+        <v>2</v>
+      </c>
+      <c r="G100" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D100" s="5">
-        <v>2</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F100" s="5">
-        <v>2</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="H100" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="101" spans="1:32" ht="30" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -9359,12 +9353,12 @@
       <c r="E101" s="12"/>
       <c r="F101" s="12"/>
       <c r="G101" s="12"/>
-      <c r="H101" s="58" t="s">
-        <v>160</v>
-      </c>
-      <c r="I101" s="58"/>
-      <c r="J101" s="58"/>
-      <c r="K101" s="58"/>
+      <c r="H101" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="I101" s="57"/>
+      <c r="J101" s="57"/>
+      <c r="K101" s="57"/>
       <c r="L101" s="12"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12"/>
@@ -9386,7 +9380,7 @@
       <c r="AD101" s="12"/>
       <c r="AE101" s="12"/>
     </row>
-    <row r="102" spans="1:32" ht="15.75" customHeight="1">
+    <row r="102" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -9395,7 +9389,7 @@
       <c r="F102" s="12"/>
       <c r="G102" s="12"/>
       <c r="H102" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="13"/>
@@ -9421,7 +9415,7 @@
       <c r="AD102" s="12"/>
       <c r="AE102" s="12"/>
     </row>
-    <row r="103" spans="1:32" ht="24" customHeight="1">
+    <row r="103" spans="1:32" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -9430,11 +9424,11 @@
       <c r="F103" s="12"/>
       <c r="G103" s="12"/>
       <c r="H103" s="14"/>
-      <c r="I103" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="J103" s="59"/>
-      <c r="K103" s="59"/>
+      <c r="I103" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="J103" s="58"/>
+      <c r="K103" s="58"/>
       <c r="L103" s="12"/>
       <c r="M103" s="12"/>
       <c r="N103" s="12"/>
@@ -9456,7 +9450,7 @@
       <c r="AD103" s="12"/>
       <c r="AE103" s="12"/>
     </row>
-    <row r="104" spans="1:32" ht="18" customHeight="1">
+    <row r="104" spans="1:32" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -9466,10 +9460,10 @@
       <c r="G104" s="12"/>
       <c r="H104" s="15" t="str">
         <f>COUNTIF(H105:H136,1)&amp;"/16"</f>
-        <v>1/16</v>
+        <v>16/16</v>
       </c>
       <c r="I104" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J104" s="12"/>
       <c r="K104" s="17"/>
@@ -9494,7 +9488,7 @@
       <c r="AD104" s="12"/>
       <c r="AE104" s="12"/>
     </row>
-    <row r="105" spans="1:32" ht="21.75" customHeight="1">
+    <row r="105" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -9513,9 +9507,7 @@
         <f>IF(H105=1,COUNTIF($H$105:H105,1),"")</f>
         <v>1</v>
       </c>
-      <c r="K105" s="20" t="s">
-        <v>163</v>
-      </c>
+      <c r="K105" s="20"/>
       <c r="L105" s="12"/>
       <c r="M105" s="12"/>
       <c r="N105" s="12"/>
@@ -9537,7 +9529,7 @@
       <c r="AD105" s="12"/>
       <c r="AE105" s="12"/>
     </row>
-    <row r="106" spans="1:32" ht="21.75" customHeight="1">
+    <row r="106" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -9576,7 +9568,7 @@
       <c r="AD106" s="12"/>
       <c r="AE106" s="12"/>
     </row>
-    <row r="107" spans="1:32" ht="21.75" customHeight="1">
+    <row r="107" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -9585,7 +9577,7 @@
       <c r="F107" s="12"/>
       <c r="G107" s="12"/>
       <c r="H107" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I107" s="19" t="str">
         <f>IFERROR(M15,"B1")</f>
@@ -9595,7 +9587,7 @@
         <v>2</v>
       </c>
       <c r="K107" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L107" s="12"/>
       <c r="M107" s="12"/>
@@ -9618,7 +9610,7 @@
       <c r="AD107" s="12"/>
       <c r="AE107" s="12"/>
     </row>
-    <row r="108" spans="1:32" ht="21.75" customHeight="1">
+    <row r="108" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -9657,7 +9649,7 @@
       <c r="AD108" s="12"/>
       <c r="AE108" s="12"/>
     </row>
-    <row r="109" spans="1:32" ht="21.75" customHeight="1">
+    <row r="109" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -9666,7 +9658,7 @@
       <c r="F109" s="12"/>
       <c r="G109" s="12"/>
       <c r="H109" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I109" s="19" t="str">
         <f>IFERROR(M23,"C1")</f>
@@ -9676,7 +9668,7 @@
         <v>3</v>
       </c>
       <c r="K109" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L109" s="12"/>
       <c r="M109" s="12"/>
@@ -9699,7 +9691,7 @@
       <c r="AD109" s="12"/>
       <c r="AE109" s="12"/>
     </row>
-    <row r="110" spans="1:32" ht="21.75" customHeight="1">
+    <row r="110" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -9708,7 +9700,7 @@
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
       <c r="H110" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I110" s="22" t="str">
         <f>IFERROR(M24,"C2")</f>
@@ -9718,7 +9710,7 @@
         <v>4</v>
       </c>
       <c r="K110" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L110" s="12"/>
       <c r="M110" s="12"/>
@@ -9741,7 +9733,7 @@
       <c r="AD110" s="12"/>
       <c r="AE110" s="12"/>
     </row>
-    <row r="111" spans="1:32" ht="21.75" customHeight="1">
+    <row r="111" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -9780,7 +9772,7 @@
       <c r="AD111" s="12"/>
       <c r="AE111" s="12"/>
     </row>
-    <row r="112" spans="1:32" ht="21.75" customHeight="1">
+    <row r="112" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -9789,7 +9781,7 @@
       <c r="F112" s="12"/>
       <c r="G112" s="12"/>
       <c r="H112" s="21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I112" s="22" t="str">
         <f>IFERROR(M32,"D2")</f>
@@ -9799,7 +9791,7 @@
         <v>5</v>
       </c>
       <c r="K112" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L112" s="12"/>
       <c r="M112" s="12"/>
@@ -9822,7 +9814,7 @@
       <c r="AD112" s="12"/>
       <c r="AE112" s="12"/>
     </row>
-    <row r="113" spans="1:31" ht="21.75" customHeight="1">
+    <row r="113" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -9831,7 +9823,7 @@
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
       <c r="H113" s="18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I113" s="19" t="str">
         <f>IFERROR(M39,"E1")</f>
@@ -9841,7 +9833,7 @@
         <v>6</v>
       </c>
       <c r="K113" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L113" s="12"/>
       <c r="M113" s="12"/>
@@ -9864,7 +9856,7 @@
       <c r="AD113" s="12"/>
       <c r="AE113" s="12"/>
     </row>
-    <row r="114" spans="1:31" ht="21.75" customHeight="1">
+    <row r="114" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -9903,7 +9895,7 @@
       <c r="AD114" s="12"/>
       <c r="AE114" s="12"/>
     </row>
-    <row r="115" spans="1:31" ht="21.75" customHeight="1">
+    <row r="115" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -9912,7 +9904,7 @@
       <c r="F115" s="12"/>
       <c r="G115" s="12"/>
       <c r="H115" s="18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I115" s="19" t="str">
         <f>IFERROR(M47,"F1")</f>
@@ -9922,7 +9914,7 @@
         <v>7</v>
       </c>
       <c r="K115" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L115" s="12"/>
       <c r="M115" s="12"/>
@@ -9945,7 +9937,7 @@
       <c r="AD115" s="12"/>
       <c r="AE115" s="12"/>
     </row>
-    <row r="116" spans="1:31" ht="21.75" customHeight="1">
+    <row r="116" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -9984,7 +9976,7 @@
       <c r="AD116" s="12"/>
       <c r="AE116" s="12"/>
     </row>
-    <row r="117" spans="1:31" ht="21.75" customHeight="1">
+    <row r="117" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -9993,7 +9985,7 @@
       <c r="F117" s="12"/>
       <c r="G117" s="12"/>
       <c r="H117" s="18">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I117" s="19" t="str">
         <f>IFERROR(M55,"G1")</f>
@@ -10003,7 +9995,7 @@
         <v>8</v>
       </c>
       <c r="K117" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L117" s="12"/>
       <c r="M117" s="12"/>
@@ -10026,7 +10018,7 @@
       <c r="AD117" s="12"/>
       <c r="AE117" s="12"/>
     </row>
-    <row r="118" spans="1:31" ht="21.75" customHeight="1">
+    <row r="118" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -10035,7 +10027,7 @@
       <c r="F118" s="12"/>
       <c r="G118" s="12"/>
       <c r="H118" s="21">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I118" s="22" t="str">
         <f>IFERROR(M56,"G2")</f>
@@ -10045,7 +10037,7 @@
         <v>9</v>
       </c>
       <c r="K118" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L118" s="12"/>
       <c r="M118" s="12"/>
@@ -10068,7 +10060,7 @@
       <c r="AD118" s="12"/>
       <c r="AE118" s="12"/>
     </row>
-    <row r="119" spans="1:31" ht="21.75" customHeight="1">
+    <row r="119" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -10077,7 +10069,7 @@
       <c r="F119" s="12"/>
       <c r="G119" s="12"/>
       <c r="H119" s="18">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I119" s="19" t="str">
         <f>IFERROR(M63,"H1")</f>
@@ -10087,7 +10079,7 @@
         <v>10</v>
       </c>
       <c r="K119" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L119" s="12"/>
       <c r="M119" s="12"/>
@@ -10110,7 +10102,7 @@
       <c r="AD119" s="12"/>
       <c r="AE119" s="12"/>
     </row>
-    <row r="120" spans="1:31" ht="21.75" customHeight="1">
+    <row r="120" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -10149,7 +10141,7 @@
       <c r="AD120" s="12"/>
       <c r="AE120" s="12"/>
     </row>
-    <row r="121" spans="1:31" ht="21.75" customHeight="1">
+    <row r="121" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -10158,7 +10150,7 @@
       <c r="F121" s="12"/>
       <c r="G121" s="12"/>
       <c r="H121" s="18">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I121" s="19" t="str">
         <f>IFERROR(M71,"I1")</f>
@@ -10168,7 +10160,7 @@
         <v>11</v>
       </c>
       <c r="K121" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L121" s="12"/>
       <c r="M121" s="12"/>
@@ -10191,7 +10183,7 @@
       <c r="AD121" s="12"/>
       <c r="AE121" s="12"/>
     </row>
-    <row r="122" spans="1:31" ht="21.75" customHeight="1">
+    <row r="122" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="12"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
@@ -10230,7 +10222,7 @@
       <c r="AD122" s="12"/>
       <c r="AE122" s="12"/>
     </row>
-    <row r="123" spans="1:31" ht="21.75" customHeight="1">
+    <row r="123" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="12"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
@@ -10239,7 +10231,7 @@
       <c r="F123" s="12"/>
       <c r="G123" s="12"/>
       <c r="H123" s="18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I123" s="19" t="str">
         <f>IFERROR(M79,"J1")</f>
@@ -10249,7 +10241,7 @@
         <v>12</v>
       </c>
       <c r="K123" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L123" s="12"/>
       <c r="M123" s="12"/>
@@ -10272,7 +10264,7 @@
       <c r="AD123" s="12"/>
       <c r="AE123" s="12"/>
     </row>
-    <row r="124" spans="1:31" ht="21.75" customHeight="1">
+    <row r="124" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="12"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
@@ -10311,7 +10303,7 @@
       <c r="AD124" s="12"/>
       <c r="AE124" s="12"/>
     </row>
-    <row r="125" spans="1:31" ht="21.75" customHeight="1">
+    <row r="125" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
@@ -10320,7 +10312,7 @@
       <c r="F125" s="12"/>
       <c r="G125" s="12"/>
       <c r="H125" s="18">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I125" s="19" t="str">
         <f>IFERROR(M87,"K1")</f>
@@ -10330,7 +10322,7 @@
         <v>13</v>
       </c>
       <c r="K125" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L125" s="12"/>
       <c r="M125" s="12"/>
@@ -10353,7 +10345,7 @@
       <c r="AD125" s="12"/>
       <c r="AE125" s="12"/>
     </row>
-    <row r="126" spans="1:31" ht="21.75" customHeight="1">
+    <row r="126" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -10392,7 +10384,7 @@
       <c r="AD126" s="12"/>
       <c r="AE126" s="12"/>
     </row>
-    <row r="127" spans="1:31" ht="21.75" customHeight="1">
+    <row r="127" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
@@ -10401,7 +10393,7 @@
       <c r="F127" s="12"/>
       <c r="G127" s="12"/>
       <c r="H127" s="18">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I127" s="19" t="str">
         <f>IFERROR(M95,"L1")</f>
@@ -10411,7 +10403,7 @@
         <v>14</v>
       </c>
       <c r="K127" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L127" s="12"/>
       <c r="M127" s="12"/>
@@ -10434,7 +10426,7 @@
       <c r="AD127" s="12"/>
       <c r="AE127" s="12"/>
     </row>
-    <row r="128" spans="1:31" ht="21.75" customHeight="1">
+    <row r="128" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
@@ -10443,7 +10435,7 @@
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
       <c r="H128" s="21">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I128" s="22" t="str">
         <f>IFERROR(M96,"L2")</f>
@@ -10453,7 +10445,7 @@
         <v>15</v>
       </c>
       <c r="K128" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L128" s="12"/>
       <c r="M128" s="12"/>
@@ -10476,7 +10468,7 @@
       <c r="AD128" s="12"/>
       <c r="AE128" s="12"/>
     </row>
-    <row r="129" spans="1:31" ht="21.75" customHeight="1">
+    <row r="129" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -10485,7 +10477,7 @@
       <c r="F129" s="12"/>
       <c r="G129" s="12"/>
       <c r="H129" s="18">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I129" s="19" t="str">
         <f>IFERROR(INDEX($A$300:$A$311,MATCH(1,$E$300:$E$311,0)),"")</f>
@@ -10495,7 +10487,7 @@
         <v>16</v>
       </c>
       <c r="K129" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L129" s="12"/>
       <c r="M129" s="12"/>
@@ -10518,7 +10510,7 @@
       <c r="AD129" s="12"/>
       <c r="AE129" s="12"/>
     </row>
-    <row r="130" spans="1:31" ht="21.75" customHeight="1">
+    <row r="130" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -10532,7 +10524,7 @@
         <v>Colombia</v>
       </c>
       <c r="J130" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K130" s="23"/>
       <c r="L130" s="12"/>
@@ -10556,7 +10548,7 @@
       <c r="AD130" s="12"/>
       <c r="AE130" s="12"/>
     </row>
-    <row r="131" spans="1:31" ht="21.75" customHeight="1">
+    <row r="131" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
@@ -10595,7 +10587,7 @@
       <c r="AD131" s="12"/>
       <c r="AE131" s="12"/>
     </row>
-    <row r="132" spans="1:31" ht="21.75" customHeight="1">
+    <row r="132" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
@@ -10634,7 +10626,7 @@
       <c r="AD132" s="12"/>
       <c r="AE132" s="12"/>
     </row>
-    <row r="133" spans="1:31" ht="21.75" customHeight="1">
+    <row r="133" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
@@ -10673,7 +10665,7 @@
       <c r="AD133" s="12"/>
       <c r="AE133" s="12"/>
     </row>
-    <row r="134" spans="1:31" ht="21.75" customHeight="1">
+    <row r="134" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -10712,7 +10704,7 @@
       <c r="AD134" s="12"/>
       <c r="AE134" s="12"/>
     </row>
-    <row r="135" spans="1:31" ht="21.75" customHeight="1">
+    <row r="135" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -10751,7 +10743,7 @@
       <c r="AD135" s="12"/>
       <c r="AE135" s="12"/>
     </row>
-    <row r="136" spans="1:31" ht="21.75" customHeight="1">
+    <row r="136" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -10790,7 +10782,7 @@
       <c r="AD136" s="12"/>
       <c r="AE136" s="12"/>
     </row>
-    <row r="137" spans="1:31" ht="6" customHeight="1">
+    <row r="137" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="12"/>
       <c r="B137" s="12"/>
       <c r="C137" s="12"/>
@@ -10823,7 +10815,7 @@
       <c r="AD137" s="12"/>
       <c r="AE137" s="12"/>
     </row>
-    <row r="138" spans="1:31" ht="24" customHeight="1">
+    <row r="138" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="12"/>
       <c r="B138" s="12"/>
       <c r="C138" s="12"/>
@@ -10832,11 +10824,11 @@
       <c r="F138" s="12"/>
       <c r="G138" s="12"/>
       <c r="H138" s="25"/>
-      <c r="I138" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="J138" s="60"/>
-      <c r="K138" s="60"/>
+      <c r="I138" s="59" t="s">
+        <v>163</v>
+      </c>
+      <c r="J138" s="59"/>
+      <c r="K138" s="59"/>
       <c r="L138" s="12"/>
       <c r="M138" s="12"/>
       <c r="N138" s="12"/>
@@ -10858,7 +10850,7 @@
       <c r="AD138" s="12"/>
       <c r="AE138" s="12"/>
     </row>
-    <row r="139" spans="1:31" ht="18" customHeight="1">
+    <row r="139" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="12"/>
       <c r="C139" s="12"/>
@@ -10868,10 +10860,10 @@
       <c r="G139" s="12"/>
       <c r="H139" s="15" t="str">
         <f>COUNTIF(H140:H155,1)&amp;"/8"</f>
-        <v>1/8</v>
+        <v>5/8</v>
       </c>
       <c r="I139" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J139" s="12"/>
       <c r="K139" s="17"/>
@@ -10896,7 +10888,7 @@
       <c r="AD139" s="12"/>
       <c r="AE139" s="12"/>
     </row>
-    <row r="140" spans="1:31" ht="21.75" customHeight="1">
+    <row r="140" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="12"/>
       <c r="B140" s="12"/>
       <c r="C140" s="12"/>
@@ -10908,7 +10900,7 @@
         <v>1</v>
       </c>
       <c r="I140" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J140" s="12">
         <f>IF(H140=1,COUNTIF($H$140:H140,1),"")</f>
@@ -10936,7 +10928,7 @@
       <c r="AD140" s="12"/>
       <c r="AE140" s="12"/>
     </row>
-    <row r="141" spans="1:31" ht="21.75" customHeight="1">
+    <row r="141" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="12"/>
       <c r="B141" s="12"/>
       <c r="C141" s="12"/>
@@ -10948,7 +10940,7 @@
         <v>2</v>
       </c>
       <c r="I141" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J141" s="12">
         <v>2</v>
@@ -10975,7 +10967,7 @@
       <c r="AD141" s="12"/>
       <c r="AE141" s="12"/>
     </row>
-    <row r="142" spans="1:31" ht="21.75" customHeight="1">
+    <row r="142" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="12"/>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
@@ -10984,10 +10976,10 @@
       <c r="F142" s="12"/>
       <c r="G142" s="12"/>
       <c r="H142" s="26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I142" s="27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J142" s="12">
         <v>3</v>
@@ -11014,7 +11006,7 @@
       <c r="AD142" s="12"/>
       <c r="AE142" s="12"/>
     </row>
-    <row r="143" spans="1:31" ht="21.75" customHeight="1">
+    <row r="143" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12"/>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
@@ -11023,10 +11015,10 @@
       <c r="F143" s="12"/>
       <c r="G143" s="12"/>
       <c r="H143" s="29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I143" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J143" s="12">
         <v>4</v>
@@ -11053,7 +11045,7 @@
       <c r="AD143" s="12"/>
       <c r="AE143" s="12"/>
     </row>
-    <row r="144" spans="1:31" ht="21.75" customHeight="1">
+    <row r="144" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="12"/>
       <c r="B144" s="12"/>
       <c r="C144" s="12"/>
@@ -11062,10 +11054,10 @@
       <c r="F144" s="12"/>
       <c r="G144" s="12"/>
       <c r="H144" s="26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I144" s="27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J144" s="12">
         <v>5</v>
@@ -11092,7 +11084,7 @@
       <c r="AD144" s="12"/>
       <c r="AE144" s="12"/>
     </row>
-    <row r="145" spans="1:31" ht="21.75" customHeight="1">
+    <row r="145" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="12"/>
       <c r="B145" s="12"/>
       <c r="C145" s="12"/>
@@ -11104,7 +11096,7 @@
         <v>6</v>
       </c>
       <c r="I145" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J145" s="12">
         <v>6</v>
@@ -11131,7 +11123,7 @@
       <c r="AD145" s="12"/>
       <c r="AE145" s="12"/>
     </row>
-    <row r="146" spans="1:31" ht="21.75" customHeight="1">
+    <row r="146" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="12"/>
       <c r="B146" s="12"/>
       <c r="C146" s="12"/>
@@ -11143,7 +11135,7 @@
         <v>7</v>
       </c>
       <c r="I146" s="27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J146" s="12">
         <v>7</v>
@@ -11170,7 +11162,7 @@
       <c r="AD146" s="12"/>
       <c r="AE146" s="12"/>
     </row>
-    <row r="147" spans="1:31" ht="21.75" customHeight="1">
+    <row r="147" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="12"/>
       <c r="B147" s="12"/>
       <c r="C147" s="12"/>
@@ -11179,10 +11171,10 @@
       <c r="F147" s="12"/>
       <c r="G147" s="12"/>
       <c r="H147" s="29">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I147" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J147" s="12">
         <v>8</v>
@@ -11209,7 +11201,7 @@
       <c r="AD147" s="12"/>
       <c r="AE147" s="12"/>
     </row>
-    <row r="148" spans="1:31" ht="21.75" customHeight="1">
+    <row r="148" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="12"/>
       <c r="B148" s="12"/>
       <c r="C148" s="12"/>
@@ -11245,7 +11237,7 @@
       <c r="AD148" s="12"/>
       <c r="AE148" s="12"/>
     </row>
-    <row r="149" spans="1:31" ht="21.75" customHeight="1">
+    <row r="149" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
       <c r="B149" s="12"/>
       <c r="C149" s="12"/>
@@ -11281,7 +11273,7 @@
       <c r="AD149" s="12"/>
       <c r="AE149" s="12"/>
     </row>
-    <row r="150" spans="1:31" ht="21.75" customHeight="1">
+    <row r="150" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="12"/>
       <c r="B150" s="12"/>
       <c r="C150" s="12"/>
@@ -11317,7 +11309,7 @@
       <c r="AD150" s="12"/>
       <c r="AE150" s="12"/>
     </row>
-    <row r="151" spans="1:31" ht="21.75" customHeight="1">
+    <row r="151" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="12"/>
       <c r="B151" s="12"/>
       <c r="C151" s="12"/>
@@ -11353,7 +11345,7 @@
       <c r="AD151" s="12"/>
       <c r="AE151" s="12"/>
     </row>
-    <row r="152" spans="1:31" ht="21.75" customHeight="1">
+    <row r="152" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12"/>
       <c r="B152" s="12"/>
       <c r="C152" s="12"/>
@@ -11389,7 +11381,7 @@
       <c r="AD152" s="12"/>
       <c r="AE152" s="12"/>
     </row>
-    <row r="153" spans="1:31" ht="21.75" customHeight="1">
+    <row r="153" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="12"/>
       <c r="B153" s="12"/>
       <c r="C153" s="12"/>
@@ -11425,7 +11417,7 @@
       <c r="AD153" s="12"/>
       <c r="AE153" s="12"/>
     </row>
-    <row r="154" spans="1:31" ht="21.75" customHeight="1">
+    <row r="154" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="12"/>
       <c r="B154" s="12"/>
       <c r="C154" s="12"/>
@@ -11461,7 +11453,7 @@
       <c r="AD154" s="12"/>
       <c r="AE154" s="12"/>
     </row>
-    <row r="155" spans="1:31" ht="21.75" customHeight="1">
+    <row r="155" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="12"/>
       <c r="B155" s="12"/>
       <c r="C155" s="12"/>
@@ -11497,7 +11489,7 @@
       <c r="AD155" s="12"/>
       <c r="AE155" s="12"/>
     </row>
-    <row r="156" spans="1:31" ht="6" customHeight="1">
+    <row r="156" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12"/>
       <c r="B156" s="12"/>
       <c r="C156" s="12"/>
@@ -11530,7 +11522,7 @@
       <c r="AD156" s="12"/>
       <c r="AE156" s="12"/>
     </row>
-    <row r="157" spans="1:31" ht="24" customHeight="1">
+    <row r="157" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="12"/>
       <c r="B157" s="12"/>
       <c r="C157" s="12"/>
@@ -11539,11 +11531,11 @@
       <c r="F157" s="12"/>
       <c r="G157" s="12"/>
       <c r="H157" s="32"/>
-      <c r="I157" s="53" t="s">
-        <v>165</v>
-      </c>
-      <c r="J157" s="53"/>
-      <c r="K157" s="53"/>
+      <c r="I157" s="52" t="s">
+        <v>164</v>
+      </c>
+      <c r="J157" s="52"/>
+      <c r="K157" s="52"/>
       <c r="L157" s="12"/>
       <c r="M157" s="12"/>
       <c r="N157" s="12"/>
@@ -11565,7 +11557,7 @@
       <c r="AD157" s="12"/>
       <c r="AE157" s="12"/>
     </row>
-    <row r="158" spans="1:31" ht="18" customHeight="1">
+    <row r="158" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="12"/>
       <c r="B158" s="12"/>
       <c r="C158" s="12"/>
@@ -11575,10 +11567,10 @@
       <c r="G158" s="12"/>
       <c r="H158" s="15" t="str">
         <f>COUNTIF(H159:H166,1)&amp;"/4"</f>
-        <v>1/4</v>
+        <v>4/4</v>
       </c>
       <c r="I158" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J158" s="12"/>
       <c r="K158" s="17"/>
@@ -11603,7 +11595,7 @@
       <c r="AD158" s="12"/>
       <c r="AE158" s="12"/>
     </row>
-    <row r="159" spans="1:31" ht="21.75" customHeight="1">
+    <row r="159" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="12"/>
       <c r="B159" s="12"/>
       <c r="C159" s="12"/>
@@ -11615,7 +11607,7 @@
         <v>1</v>
       </c>
       <c r="I159" s="34" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J159" s="12">
         <f>IF(H159=1,COUNTIF($H$159:H159,1),"")</f>
@@ -11643,7 +11635,7 @@
       <c r="AD159" s="12"/>
       <c r="AE159" s="12"/>
     </row>
-    <row r="160" spans="1:31" ht="21.75" customHeight="1">
+    <row r="160" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="12"/>
       <c r="B160" s="12"/>
       <c r="C160" s="12"/>
@@ -11652,14 +11644,14 @@
       <c r="F160" s="12"/>
       <c r="G160" s="12"/>
       <c r="H160" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I160" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="J160" s="12" t="str">
+        <v>67</v>
+      </c>
+      <c r="J160" s="12">
         <f>IF(H160=1,COUNTIF($H$159:H160,1),"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K160" s="38"/>
       <c r="L160" s="12"/>
@@ -11683,7 +11675,7 @@
       <c r="AD160" s="12"/>
       <c r="AE160" s="12"/>
     </row>
-    <row r="161" spans="1:31" ht="21.75" customHeight="1">
+    <row r="161" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="12"/>
       <c r="C161" s="12"/>
@@ -11692,14 +11684,14 @@
       <c r="F161" s="12"/>
       <c r="G161" s="12"/>
       <c r="H161" s="33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I161" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="J161" s="12" t="str">
+        <v>123</v>
+      </c>
+      <c r="J161" s="12">
         <f>IF(H161=1,COUNTIF($H$159:H161,1),"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="K161" s="35"/>
       <c r="L161" s="12"/>
@@ -11723,7 +11715,7 @@
       <c r="AD161" s="12"/>
       <c r="AE161" s="12"/>
     </row>
-    <row r="162" spans="1:31" ht="21.75" customHeight="1">
+    <row r="162" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="12"/>
       <c r="B162" s="12"/>
       <c r="C162" s="12"/>
@@ -11732,14 +11724,14 @@
       <c r="F162" s="12"/>
       <c r="G162" s="12"/>
       <c r="H162" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I162" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="J162" s="12" t="str">
+        <v>133</v>
+      </c>
+      <c r="J162" s="12">
         <f>IF(H162=1,COUNTIF($H$159:H162,1),"")</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K162" s="38"/>
       <c r="L162" s="12"/>
@@ -11763,7 +11755,7 @@
       <c r="AD162" s="12"/>
       <c r="AE162" s="12"/>
     </row>
-    <row r="163" spans="1:31" ht="21.75" customHeight="1">
+    <row r="163" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="12"/>
       <c r="B163" s="12"/>
       <c r="C163" s="12"/>
@@ -11799,7 +11791,7 @@
       <c r="AD163" s="12"/>
       <c r="AE163" s="12"/>
     </row>
-    <row r="164" spans="1:31" ht="21.75" customHeight="1">
+    <row r="164" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="12"/>
       <c r="B164" s="12"/>
       <c r="C164" s="12"/>
@@ -11835,7 +11827,7 @@
       <c r="AD164" s="12"/>
       <c r="AE164" s="12"/>
     </row>
-    <row r="165" spans="1:31" ht="21.75" customHeight="1">
+    <row r="165" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="12"/>
       <c r="B165" s="12"/>
       <c r="C165" s="12"/>
@@ -11871,7 +11863,7 @@
       <c r="AD165" s="12"/>
       <c r="AE165" s="12"/>
     </row>
-    <row r="166" spans="1:31" ht="21.75" customHeight="1">
+    <row r="166" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12"/>
       <c r="B166" s="12"/>
       <c r="C166" s="12"/>
@@ -11910,7 +11902,7 @@
       <c r="AD166" s="12"/>
       <c r="AE166" s="12"/>
     </row>
-    <row r="167" spans="1:31" ht="6" customHeight="1">
+    <row r="167" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="12"/>
       <c r="B167" s="12"/>
       <c r="C167" s="12"/>
@@ -11943,7 +11935,7 @@
       <c r="AD167" s="12"/>
       <c r="AE167" s="12"/>
     </row>
-    <row r="168" spans="1:31" ht="24" customHeight="1">
+    <row r="168" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="12"/>
       <c r="B168" s="12"/>
       <c r="C168" s="12"/>
@@ -11952,11 +11944,11 @@
       <c r="F168" s="12"/>
       <c r="G168" s="12"/>
       <c r="H168" s="39"/>
-      <c r="I168" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="J168" s="54"/>
-      <c r="K168" s="54"/>
+      <c r="I168" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="J168" s="53"/>
+      <c r="K168" s="53"/>
       <c r="L168" s="12"/>
       <c r="M168" s="12"/>
       <c r="N168" s="12"/>
@@ -11978,7 +11970,7 @@
       <c r="AD168" s="12"/>
       <c r="AE168" s="12"/>
     </row>
-    <row r="169" spans="1:31" ht="18" customHeight="1">
+    <row r="169" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="12"/>
       <c r="C169" s="12"/>
@@ -11988,10 +11980,10 @@
       <c r="G169" s="12"/>
       <c r="H169" s="15" t="str">
         <f>COUNTIF(H170:H173,1)&amp;"/2"</f>
-        <v>1/2</v>
+        <v>2/2</v>
       </c>
       <c r="I169" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J169" s="12"/>
       <c r="K169" s="17"/>
@@ -12016,7 +12008,7 @@
       <c r="AD169" s="12"/>
       <c r="AE169" s="12"/>
     </row>
-    <row r="170" spans="1:31" ht="21.75" customHeight="1">
+    <row r="170" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="12"/>
       <c r="B170" s="12"/>
       <c r="C170" s="12"/>
@@ -12057,7 +12049,7 @@
       <c r="AD170" s="12"/>
       <c r="AE170" s="12"/>
     </row>
-    <row r="171" spans="1:31" ht="21.75" customHeight="1">
+    <row r="171" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="12"/>
       <c r="B171" s="12"/>
       <c r="C171" s="12"/>
@@ -12066,10 +12058,10 @@
       <c r="F171" s="12"/>
       <c r="G171" s="12"/>
       <c r="H171" s="43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I171" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J171" s="12">
         <v>2</v>
@@ -12096,7 +12088,7 @@
       <c r="AD171" s="12"/>
       <c r="AE171" s="12"/>
     </row>
-    <row r="172" spans="1:31" ht="21.75" customHeight="1">
+    <row r="172" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="12"/>
       <c r="C172" s="12"/>
@@ -12107,7 +12099,7 @@
       <c r="H172" s="40"/>
       <c r="I172" s="41" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(3,$J$159:$J$166,0)),"")</f>
-        <v/>
+        <v>Spania</v>
       </c>
       <c r="J172" s="12" t="str">
         <f>IF(H172=1,COUNTIF($H$170:H172,1),"")</f>
@@ -12135,7 +12127,7 @@
       <c r="AD172" s="12"/>
       <c r="AE172" s="12"/>
     </row>
-    <row r="173" spans="1:31" ht="21.75" customHeight="1">
+    <row r="173" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="12"/>
       <c r="B173" s="12"/>
       <c r="C173" s="12"/>
@@ -12146,7 +12138,7 @@
       <c r="H173" s="43"/>
       <c r="I173" s="44" t="str">
         <f>IFERROR(INDEX($I$159:$I$166,MATCH(4,$J$159:$J$166,0)),"")</f>
-        <v/>
+        <v>Norge</v>
       </c>
       <c r="J173" s="12" t="str">
         <f>IF(H173=1,COUNTIF($H$170:H173,1),"")</f>
@@ -12174,7 +12166,7 @@
       <c r="AD173" s="12"/>
       <c r="AE173" s="12"/>
     </row>
-    <row r="174" spans="1:31" ht="6" customHeight="1">
+    <row r="174" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="12"/>
       <c r="B174" s="12"/>
       <c r="C174" s="12"/>
@@ -12207,7 +12199,7 @@
       <c r="AD174" s="12"/>
       <c r="AE174" s="12"/>
     </row>
-    <row r="175" spans="1:31" ht="24" customHeight="1">
+    <row r="175" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="12"/>
       <c r="B175" s="12"/>
       <c r="C175" s="12"/>
@@ -12216,11 +12208,11 @@
       <c r="F175" s="12"/>
       <c r="G175" s="12"/>
       <c r="H175" s="46"/>
-      <c r="I175" s="55" t="s">
-        <v>167</v>
-      </c>
-      <c r="J175" s="55"/>
-      <c r="K175" s="55"/>
+      <c r="I175" s="54" t="s">
+        <v>166</v>
+      </c>
+      <c r="J175" s="54"/>
+      <c r="K175" s="54"/>
       <c r="L175" s="12"/>
       <c r="M175" s="12"/>
       <c r="N175" s="12"/>
@@ -12242,7 +12234,7 @@
       <c r="AD175" s="12"/>
       <c r="AE175" s="12"/>
     </row>
-    <row r="176" spans="1:31" ht="18" customHeight="1">
+    <row r="176" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12"/>
       <c r="B176" s="12"/>
       <c r="C176" s="12"/>
@@ -12255,7 +12247,7 @@
         <v>1/1</v>
       </c>
       <c r="I176" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J176" s="12"/>
       <c r="K176" s="17"/>
@@ -12280,7 +12272,7 @@
       <c r="AD176" s="12"/>
       <c r="AE176" s="12"/>
     </row>
-    <row r="177" spans="1:31" ht="21.75" customHeight="1">
+    <row r="177" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="12"/>
       <c r="B177" s="12"/>
       <c r="C177" s="12"/>
@@ -12291,14 +12283,15 @@
       <c r="H177" s="47">
         <v>1</v>
       </c>
-      <c r="I177" s="48" t="s">
-        <v>168</v>
+      <c r="I177" s="50" t="str">
+        <f>IFERROR(INDEX($I$170:$I$173,MATCH(1,$J$170:$J$173,0)),"")</f>
+        <v>Argentina</v>
       </c>
       <c r="J177" s="12">
         <f>IF(H177=1,COUNTIF($H$177:H177,1),"")</f>
         <v>1</v>
       </c>
-      <c r="K177" s="49"/>
+      <c r="K177" s="48"/>
       <c r="L177" s="12"/>
       <c r="M177" s="12"/>
       <c r="N177" s="12"/>
@@ -12320,7 +12313,7 @@
       <c r="AD177" s="12"/>
       <c r="AE177" s="12"/>
     </row>
-    <row r="178" spans="1:31" ht="21.75" customHeight="1">
+    <row r="178" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="12"/>
       <c r="B178" s="12"/>
       <c r="C178" s="12"/>
@@ -12328,8 +12321,8 @@
       <c r="E178" s="12"/>
       <c r="F178" s="12"/>
       <c r="G178" s="12"/>
-      <c r="H178" s="50"/>
-      <c r="I178" s="51" t="str">
+      <c r="H178" s="49"/>
+      <c r="I178" s="50" t="str">
         <f>IFERROR(INDEX($I$170:$I$173,MATCH(2,$J$170:$J$173,0)),"")</f>
         <v>Spania</v>
       </c>
@@ -12337,7 +12330,7 @@
         <f>IF(H178=1,COUNTIF($H$177:H178,1),"")</f>
         <v/>
       </c>
-      <c r="K178" s="52"/>
+      <c r="K178" s="51"/>
       <c r="L178" s="12"/>
       <c r="M178" s="12"/>
       <c r="N178" s="12"/>
@@ -12359,7 +12352,7 @@
       <c r="AD178" s="12"/>
       <c r="AE178" s="12"/>
     </row>
-    <row r="179" spans="1:31" ht="6" customHeight="1">
+    <row r="179" spans="1:31" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="12"/>
       <c r="B179" s="12"/>
       <c r="C179" s="12"/>
@@ -12392,7 +12385,7 @@
       <c r="AD179" s="12"/>
       <c r="AE179" s="12"/>
     </row>
-    <row r="180" spans="1:31" ht="15" customHeight="1">
+    <row r="180" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12"/>
       <c r="B180" s="12"/>
       <c r="C180" s="12"/>
@@ -12425,7 +12418,7 @@
       <c r="AD180" s="12"/>
       <c r="AE180" s="12"/>
     </row>
-    <row r="181" spans="1:31" ht="15" customHeight="1">
+    <row r="181" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="12"/>
       <c r="B181" s="12"/>
       <c r="C181" s="12"/>
@@ -12458,7 +12451,7 @@
       <c r="AD181" s="12"/>
       <c r="AE181" s="12"/>
     </row>
-    <row r="182" spans="1:31" ht="15" customHeight="1">
+    <row r="182" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="12"/>
       <c r="B182" s="12"/>
       <c r="C182" s="12"/>
@@ -12491,7 +12484,7 @@
       <c r="AD182" s="12"/>
       <c r="AE182" s="12"/>
     </row>
-    <row r="183" spans="1:31" ht="15" customHeight="1">
+    <row r="183" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12"/>
       <c r="B183" s="12"/>
       <c r="C183" s="12"/>
@@ -12524,7 +12517,7 @@
       <c r="AD183" s="12"/>
       <c r="AE183" s="12"/>
     </row>
-    <row r="184" spans="1:31" ht="15" customHeight="1">
+    <row r="184" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12"/>
       <c r="B184" s="12"/>
       <c r="C184" s="12"/>
@@ -12557,7 +12550,7 @@
       <c r="AD184" s="12"/>
       <c r="AE184" s="12"/>
     </row>
-    <row r="185" spans="1:31" ht="15" customHeight="1">
+    <row r="185" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="12"/>
       <c r="B185" s="12"/>
       <c r="C185" s="12"/>
@@ -12590,7 +12583,7 @@
       <c r="AD185" s="12"/>
       <c r="AE185" s="12"/>
     </row>
-    <row r="186" spans="1:31" ht="15" customHeight="1">
+    <row r="186" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="12"/>
       <c r="B186" s="12"/>
       <c r="C186" s="12"/>
@@ -12623,7 +12616,7 @@
       <c r="AD186" s="12"/>
       <c r="AE186" s="12"/>
     </row>
-    <row r="187" spans="1:31" ht="15" customHeight="1">
+    <row r="187" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="12"/>
       <c r="B187" s="12"/>
       <c r="C187" s="12"/>
@@ -12656,7 +12649,7 @@
       <c r="AD187" s="12"/>
       <c r="AE187" s="12"/>
     </row>
-    <row r="188" spans="1:31" ht="15" customHeight="1">
+    <row r="188" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12"/>
       <c r="B188" s="12"/>
       <c r="C188" s="12"/>
@@ -12689,7 +12682,7 @@
       <c r="AD188" s="12"/>
       <c r="AE188" s="12"/>
     </row>
-    <row r="189" spans="1:31" ht="15" customHeight="1">
+    <row r="189" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12"/>
       <c r="B189" s="12"/>
       <c r="C189" s="12"/>
@@ -12722,7 +12715,7 @@
       <c r="AD189" s="12"/>
       <c r="AE189" s="12"/>
     </row>
-    <row r="190" spans="1:31" ht="15" customHeight="1">
+    <row r="190" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="12"/>
       <c r="B190" s="12"/>
       <c r="C190" s="12"/>
@@ -12755,7 +12748,7 @@
       <c r="AD190" s="12"/>
       <c r="AE190" s="12"/>
     </row>
-    <row r="191" spans="1:31" ht="15" customHeight="1">
+    <row r="191" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="12"/>
       <c r="B191" s="12"/>
       <c r="C191" s="12"/>
@@ -12788,7 +12781,7 @@
       <c r="AD191" s="12"/>
       <c r="AE191" s="12"/>
     </row>
-    <row r="192" spans="1:31" ht="15" customHeight="1">
+    <row r="192" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="12"/>
       <c r="B192" s="12"/>
       <c r="C192" s="12"/>
@@ -12821,7 +12814,7 @@
       <c r="AD192" s="12"/>
       <c r="AE192" s="12"/>
     </row>
-    <row r="193" spans="1:31" ht="15" customHeight="1">
+    <row r="193" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="12"/>
       <c r="B193" s="12"/>
       <c r="C193" s="12"/>
@@ -12854,7 +12847,7 @@
       <c r="AD193" s="12"/>
       <c r="AE193" s="12"/>
     </row>
-    <row r="194" spans="1:31" ht="15" customHeight="1">
+    <row r="194" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="12"/>
       <c r="B194" s="12"/>
       <c r="C194" s="12"/>
@@ -12887,7 +12880,7 @@
       <c r="AD194" s="12"/>
       <c r="AE194" s="12"/>
     </row>
-    <row r="195" spans="1:31" ht="15" customHeight="1">
+    <row r="195" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="12"/>
       <c r="B195" s="12"/>
       <c r="C195" s="12"/>
@@ -12920,7 +12913,7 @@
       <c r="AD195" s="12"/>
       <c r="AE195" s="12"/>
     </row>
-    <row r="196" spans="1:31" ht="15" customHeight="1">
+    <row r="196" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="12"/>
       <c r="B196" s="12"/>
       <c r="C196" s="12"/>
@@ -12953,7 +12946,7 @@
       <c r="AD196" s="12"/>
       <c r="AE196" s="12"/>
     </row>
-    <row r="197" spans="1:31" ht="15" customHeight="1">
+    <row r="197" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="12"/>
       <c r="B197" s="12"/>
       <c r="C197" s="12"/>
@@ -12986,7 +12979,7 @@
       <c r="AD197" s="12"/>
       <c r="AE197" s="12"/>
     </row>
-    <row r="198" spans="1:31" ht="15" customHeight="1">
+    <row r="198" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="12"/>
       <c r="B198" s="12"/>
       <c r="C198" s="12"/>
@@ -13019,7 +13012,7 @@
       <c r="AD198" s="12"/>
       <c r="AE198" s="12"/>
     </row>
-    <row r="199" spans="1:31" ht="15" customHeight="1">
+    <row r="199" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="12"/>
       <c r="B199" s="12"/>
       <c r="C199" s="12"/>
@@ -13052,7 +13045,7 @@
       <c r="AD199" s="12"/>
       <c r="AE199" s="12"/>
     </row>
-    <row r="200" spans="1:31" ht="15" customHeight="1">
+    <row r="200" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="12"/>
       <c r="B200" s="12"/>
       <c r="C200" s="12"/>
@@ -13085,7 +13078,7 @@
       <c r="AD200" s="12"/>
       <c r="AE200" s="12"/>
     </row>
-    <row r="201" spans="1:31" ht="15" customHeight="1">
+    <row r="201" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="12"/>
       <c r="B201" s="12"/>
       <c r="C201" s="12"/>
@@ -13118,7 +13111,7 @@
       <c r="AD201" s="12"/>
       <c r="AE201" s="12"/>
     </row>
-    <row r="202" spans="1:31" ht="15" customHeight="1">
+    <row r="202" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="12"/>
       <c r="B202" s="12"/>
       <c r="C202" s="12"/>
@@ -13151,7 +13144,7 @@
       <c r="AD202" s="12"/>
       <c r="AE202" s="12"/>
     </row>
-    <row r="203" spans="1:31" ht="15" customHeight="1">
+    <row r="203" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="12"/>
       <c r="B203" s="12"/>
       <c r="C203" s="12"/>
@@ -13184,7 +13177,7 @@
       <c r="AD203" s="12"/>
       <c r="AE203" s="12"/>
     </row>
-    <row r="204" spans="1:31" ht="15" customHeight="1">
+    <row r="204" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="12"/>
       <c r="B204" s="12"/>
       <c r="C204" s="12"/>
@@ -13217,7 +13210,7 @@
       <c r="AD204" s="12"/>
       <c r="AE204" s="12"/>
     </row>
-    <row r="205" spans="1:31" ht="15" customHeight="1">
+    <row r="205" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="12"/>
       <c r="B205" s="12"/>
       <c r="C205" s="12"/>
@@ -13250,7 +13243,7 @@
       <c r="AD205" s="12"/>
       <c r="AE205" s="12"/>
     </row>
-    <row r="206" spans="1:31" ht="15" customHeight="1">
+    <row r="206" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="12"/>
       <c r="B206" s="12"/>
       <c r="C206" s="12"/>
@@ -13283,7 +13276,7 @@
       <c r="AD206" s="12"/>
       <c r="AE206" s="12"/>
     </row>
-    <row r="207" spans="1:31" ht="15" customHeight="1">
+    <row r="207" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="12"/>
       <c r="B207" s="12"/>
       <c r="C207" s="12"/>
@@ -13316,7 +13309,7 @@
       <c r="AD207" s="12"/>
       <c r="AE207" s="12"/>
     </row>
-    <row r="208" spans="1:31" ht="15" customHeight="1">
+    <row r="208" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="12"/>
       <c r="B208" s="12"/>
       <c r="C208" s="12"/>
@@ -13349,7 +13342,7 @@
       <c r="AD208" s="12"/>
       <c r="AE208" s="12"/>
     </row>
-    <row r="209" spans="1:31" ht="15" customHeight="1">
+    <row r="209" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="12"/>
       <c r="B209" s="12"/>
       <c r="C209" s="12"/>
@@ -13382,7 +13375,7 @@
       <c r="AD209" s="12"/>
       <c r="AE209" s="12"/>
     </row>
-    <row r="210" spans="1:31" ht="15" customHeight="1">
+    <row r="210" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="12"/>
       <c r="B210" s="12"/>
       <c r="C210" s="12"/>
@@ -13415,7 +13408,7 @@
       <c r="AD210" s="12"/>
       <c r="AE210" s="12"/>
     </row>
-    <row r="211" spans="1:31" ht="15" customHeight="1">
+    <row r="211" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="12"/>
       <c r="B211" s="12"/>
       <c r="C211" s="12"/>
@@ -13448,7 +13441,7 @@
       <c r="AD211" s="12"/>
       <c r="AE211" s="12"/>
     </row>
-    <row r="212" spans="1:31" ht="15" customHeight="1">
+    <row r="212" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="12"/>
       <c r="B212" s="12"/>
       <c r="C212" s="12"/>
@@ -13481,7 +13474,7 @@
       <c r="AD212" s="12"/>
       <c r="AE212" s="12"/>
     </row>
-    <row r="213" spans="1:31" ht="15" customHeight="1">
+    <row r="213" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="12"/>
       <c r="B213" s="12"/>
       <c r="C213" s="12"/>
@@ -13514,7 +13507,7 @@
       <c r="AD213" s="12"/>
       <c r="AE213" s="12"/>
     </row>
-    <row r="214" spans="1:31" ht="15" customHeight="1">
+    <row r="214" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="12"/>
       <c r="B214" s="12"/>
       <c r="C214" s="12"/>
@@ -13547,7 +13540,7 @@
       <c r="AD214" s="12"/>
       <c r="AE214" s="12"/>
     </row>
-    <row r="215" spans="1:31" ht="15" customHeight="1">
+    <row r="215" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12"/>
       <c r="B215" s="12"/>
       <c r="C215" s="12"/>
@@ -13580,7 +13573,7 @@
       <c r="AD215" s="12"/>
       <c r="AE215" s="12"/>
     </row>
-    <row r="216" spans="1:31" ht="15" customHeight="1">
+    <row r="216" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="12"/>
       <c r="B216" s="12"/>
       <c r="C216" s="12"/>
@@ -13613,7 +13606,7 @@
       <c r="AD216" s="12"/>
       <c r="AE216" s="12"/>
     </row>
-    <row r="217" spans="1:31" ht="15" customHeight="1">
+    <row r="217" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="12"/>
       <c r="B217" s="12"/>
       <c r="C217" s="12"/>
@@ -13646,7 +13639,7 @@
       <c r="AD217" s="12"/>
       <c r="AE217" s="12"/>
     </row>
-    <row r="218" spans="1:31" ht="15" customHeight="1">
+    <row r="218" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="12"/>
       <c r="B218" s="12"/>
       <c r="C218" s="12"/>
@@ -13679,7 +13672,7 @@
       <c r="AD218" s="12"/>
       <c r="AE218" s="12"/>
     </row>
-    <row r="219" spans="1:31" ht="15" customHeight="1">
+    <row r="219" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="12"/>
       <c r="B219" s="12"/>
       <c r="C219" s="12"/>
@@ -13712,7 +13705,7 @@
       <c r="AD219" s="12"/>
       <c r="AE219" s="12"/>
     </row>
-    <row r="220" spans="1:31" ht="15" customHeight="1">
+    <row r="220" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="12"/>
       <c r="B220" s="12"/>
       <c r="C220" s="12"/>
@@ -13745,7 +13738,7 @@
       <c r="AD220" s="12"/>
       <c r="AE220" s="12"/>
     </row>
-    <row r="221" spans="1:31" ht="15" customHeight="1">
+    <row r="221" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="12"/>
       <c r="B221" s="12"/>
       <c r="C221" s="12"/>
@@ -13778,7 +13771,7 @@
       <c r="AD221" s="12"/>
       <c r="AE221" s="12"/>
     </row>
-    <row r="222" spans="1:31" ht="15" customHeight="1">
+    <row r="222" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="12"/>
       <c r="B222" s="12"/>
       <c r="C222" s="12"/>
@@ -13811,7 +13804,7 @@
       <c r="AD222" s="12"/>
       <c r="AE222" s="12"/>
     </row>
-    <row r="223" spans="1:31" ht="15" customHeight="1">
+    <row r="223" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="12"/>
       <c r="B223" s="12"/>
       <c r="C223" s="12"/>
@@ -13844,7 +13837,7 @@
       <c r="AD223" s="12"/>
       <c r="AE223" s="12"/>
     </row>
-    <row r="224" spans="1:31" ht="15" customHeight="1">
+    <row r="224" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="12"/>
       <c r="B224" s="12"/>
       <c r="C224" s="12"/>
@@ -13877,7 +13870,7 @@
       <c r="AD224" s="12"/>
       <c r="AE224" s="12"/>
     </row>
-    <row r="225" spans="1:31" ht="15" customHeight="1">
+    <row r="225" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="12"/>
       <c r="B225" s="12"/>
       <c r="C225" s="12"/>
@@ -13910,7 +13903,7 @@
       <c r="AD225" s="12"/>
       <c r="AE225" s="12"/>
     </row>
-    <row r="226" spans="1:31" ht="15" customHeight="1">
+    <row r="226" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="12"/>
       <c r="B226" s="12"/>
       <c r="C226" s="12"/>
@@ -13943,7 +13936,7 @@
       <c r="AD226" s="12"/>
       <c r="AE226" s="12"/>
     </row>
-    <row r="227" spans="1:31" ht="15" customHeight="1">
+    <row r="227" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12"/>
       <c r="B227" s="12"/>
       <c r="C227" s="12"/>
@@ -13976,7 +13969,7 @@
       <c r="AD227" s="12"/>
       <c r="AE227" s="12"/>
     </row>
-    <row r="228" spans="1:31" ht="15" customHeight="1">
+    <row r="228" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="12"/>
       <c r="B228" s="12"/>
       <c r="C228" s="12"/>
@@ -14009,7 +14002,7 @@
       <c r="AD228" s="12"/>
       <c r="AE228" s="12"/>
     </row>
-    <row r="229" spans="1:31" ht="15" customHeight="1">
+    <row r="229" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="12"/>
       <c r="B229" s="12"/>
       <c r="C229" s="12"/>
@@ -14042,7 +14035,7 @@
       <c r="AD229" s="12"/>
       <c r="AE229" s="12"/>
     </row>
-    <row r="230" spans="1:31" ht="15" customHeight="1">
+    <row r="230" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="12"/>
       <c r="B230" s="12"/>
       <c r="C230" s="12"/>
@@ -14075,7 +14068,7 @@
       <c r="AD230" s="12"/>
       <c r="AE230" s="12"/>
     </row>
-    <row r="231" spans="1:31" ht="15" customHeight="1">
+    <row r="231" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="12"/>
       <c r="B231" s="12"/>
       <c r="C231" s="12"/>
@@ -14108,7 +14101,7 @@
       <c r="AD231" s="12"/>
       <c r="AE231" s="12"/>
     </row>
-    <row r="232" spans="1:31" ht="15" customHeight="1">
+    <row r="232" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="12"/>
       <c r="B232" s="12"/>
       <c r="C232" s="12"/>
@@ -14141,7 +14134,7 @@
       <c r="AD232" s="12"/>
       <c r="AE232" s="12"/>
     </row>
-    <row r="233" spans="1:31" ht="15" customHeight="1">
+    <row r="233" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="12"/>
       <c r="B233" s="12"/>
       <c r="C233" s="12"/>
@@ -14174,7 +14167,7 @@
       <c r="AD233" s="12"/>
       <c r="AE233" s="12"/>
     </row>
-    <row r="234" spans="1:31" ht="15" customHeight="1">
+    <row r="234" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="12"/>
       <c r="B234" s="12"/>
       <c r="C234" s="12"/>
@@ -14207,7 +14200,7 @@
       <c r="AD234" s="12"/>
       <c r="AE234" s="12"/>
     </row>
-    <row r="235" spans="1:31" ht="15" customHeight="1">
+    <row r="235" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="12"/>
       <c r="B235" s="12"/>
       <c r="C235" s="12"/>
@@ -14240,7 +14233,7 @@
       <c r="AD235" s="12"/>
       <c r="AE235" s="12"/>
     </row>
-    <row r="236" spans="1:31" ht="15" customHeight="1">
+    <row r="236" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="12"/>
       <c r="B236" s="12"/>
       <c r="C236" s="12"/>
@@ -14273,7 +14266,7 @@
       <c r="AD236" s="12"/>
       <c r="AE236" s="12"/>
     </row>
-    <row r="237" spans="1:31" ht="15" customHeight="1">
+    <row r="237" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="12"/>
       <c r="B237" s="12"/>
       <c r="C237" s="12"/>
@@ -14306,7 +14299,7 @@
       <c r="AD237" s="12"/>
       <c r="AE237" s="12"/>
     </row>
-    <row r="238" spans="1:31" ht="15" customHeight="1">
+    <row r="238" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="12"/>
       <c r="B238" s="12"/>
       <c r="C238" s="12"/>
@@ -14339,7 +14332,7 @@
       <c r="AD238" s="12"/>
       <c r="AE238" s="12"/>
     </row>
-    <row r="239" spans="1:31" ht="15" customHeight="1">
+    <row r="239" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="12"/>
       <c r="B239" s="12"/>
       <c r="C239" s="12"/>
@@ -14372,7 +14365,7 @@
       <c r="AD239" s="12"/>
       <c r="AE239" s="12"/>
     </row>
-    <row r="240" spans="1:31" ht="15" customHeight="1">
+    <row r="240" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="12"/>
       <c r="B240" s="12"/>
       <c r="C240" s="12"/>
@@ -14405,7 +14398,7 @@
       <c r="AD240" s="12"/>
       <c r="AE240" s="12"/>
     </row>
-    <row r="241" spans="1:31" ht="15" customHeight="1">
+    <row r="241" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="12"/>
       <c r="B241" s="12"/>
       <c r="C241" s="12"/>
@@ -14438,7 +14431,7 @@
       <c r="AD241" s="12"/>
       <c r="AE241" s="12"/>
     </row>
-    <row r="242" spans="1:31" ht="15" customHeight="1">
+    <row r="242" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="12"/>
       <c r="B242" s="12"/>
       <c r="C242" s="12"/>
@@ -14471,7 +14464,7 @@
       <c r="AD242" s="12"/>
       <c r="AE242" s="12"/>
     </row>
-    <row r="243" spans="1:31" ht="15" customHeight="1">
+    <row r="243" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="12"/>
       <c r="B243" s="12"/>
       <c r="C243" s="12"/>
@@ -14504,7 +14497,7 @@
       <c r="AD243" s="12"/>
       <c r="AE243" s="12"/>
     </row>
-    <row r="244" spans="1:31" ht="15" customHeight="1">
+    <row r="244" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="12"/>
       <c r="B244" s="12"/>
       <c r="C244" s="12"/>
@@ -14537,7 +14530,7 @@
       <c r="AD244" s="12"/>
       <c r="AE244" s="12"/>
     </row>
-    <row r="245" spans="1:31" ht="15" customHeight="1">
+    <row r="245" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="12"/>
       <c r="B245" s="12"/>
       <c r="C245" s="12"/>
@@ -14570,7 +14563,7 @@
       <c r="AD245" s="12"/>
       <c r="AE245" s="12"/>
     </row>
-    <row r="246" spans="1:31" ht="15" customHeight="1">
+    <row r="246" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="12"/>
       <c r="B246" s="12"/>
       <c r="C246" s="12"/>
@@ -14603,7 +14596,7 @@
       <c r="AD246" s="12"/>
       <c r="AE246" s="12"/>
     </row>
-    <row r="247" spans="1:31" ht="15" customHeight="1">
+    <row r="247" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="12"/>
       <c r="B247" s="12"/>
       <c r="C247" s="12"/>
@@ -14636,7 +14629,7 @@
       <c r="AD247" s="12"/>
       <c r="AE247" s="12"/>
     </row>
-    <row r="248" spans="1:31" ht="15" customHeight="1">
+    <row r="248" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="12"/>
       <c r="B248" s="12"/>
       <c r="C248" s="12"/>
@@ -14669,7 +14662,7 @@
       <c r="AD248" s="12"/>
       <c r="AE248" s="12"/>
     </row>
-    <row r="249" spans="1:31" ht="15" customHeight="1">
+    <row r="249" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="12"/>
       <c r="B249" s="12"/>
       <c r="C249" s="12"/>
@@ -14702,7 +14695,7 @@
       <c r="AD249" s="12"/>
       <c r="AE249" s="12"/>
     </row>
-    <row r="250" spans="1:31" ht="15" customHeight="1">
+    <row r="250" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="12"/>
       <c r="B250" s="12"/>
       <c r="C250" s="12"/>
@@ -14735,7 +14728,7 @@
       <c r="AD250" s="12"/>
       <c r="AE250" s="12"/>
     </row>
-    <row r="251" spans="1:31" ht="15" customHeight="1">
+    <row r="251" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="12"/>
       <c r="B251" s="12"/>
       <c r="C251" s="12"/>
@@ -14768,7 +14761,7 @@
       <c r="AD251" s="12"/>
       <c r="AE251" s="12"/>
     </row>
-    <row r="252" spans="1:31" ht="15" customHeight="1">
+    <row r="252" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="12"/>
       <c r="B252" s="12"/>
       <c r="C252" s="12"/>
@@ -14801,7 +14794,7 @@
       <c r="AD252" s="12"/>
       <c r="AE252" s="12"/>
     </row>
-    <row r="253" spans="1:31" ht="15" customHeight="1">
+    <row r="253" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="12"/>
       <c r="B253" s="12"/>
       <c r="C253" s="12"/>
@@ -14834,7 +14827,7 @@
       <c r="AD253" s="12"/>
       <c r="AE253" s="12"/>
     </row>
-    <row r="254" spans="1:31" ht="15" customHeight="1">
+    <row r="254" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="12"/>
       <c r="B254" s="12"/>
       <c r="C254" s="12"/>
@@ -14867,7 +14860,7 @@
       <c r="AD254" s="12"/>
       <c r="AE254" s="12"/>
     </row>
-    <row r="255" spans="1:31" ht="15" customHeight="1">
+    <row r="255" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="12"/>
       <c r="B255" s="12"/>
       <c r="C255" s="12"/>
@@ -14900,7 +14893,7 @@
       <c r="AD255" s="12"/>
       <c r="AE255" s="12"/>
     </row>
-    <row r="256" spans="1:31" ht="15" customHeight="1">
+    <row r="256" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="12"/>
       <c r="B256" s="12"/>
       <c r="C256" s="12"/>
@@ -14933,7 +14926,7 @@
       <c r="AD256" s="12"/>
       <c r="AE256" s="12"/>
     </row>
-    <row r="257" spans="1:31" ht="15" customHeight="1">
+    <row r="257" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="12"/>
       <c r="B257" s="12"/>
       <c r="C257" s="12"/>
@@ -14966,7 +14959,7 @@
       <c r="AD257" s="12"/>
       <c r="AE257" s="12"/>
     </row>
-    <row r="258" spans="1:31" ht="15" customHeight="1">
+    <row r="258" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="12"/>
       <c r="B258" s="12"/>
       <c r="C258" s="12"/>
@@ -14999,7 +14992,7 @@
       <c r="AD258" s="12"/>
       <c r="AE258" s="12"/>
     </row>
-    <row r="259" spans="1:31" ht="15" customHeight="1">
+    <row r="259" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="12"/>
       <c r="B259" s="12"/>
       <c r="C259" s="12"/>
@@ -15032,7 +15025,7 @@
       <c r="AD259" s="12"/>
       <c r="AE259" s="12"/>
     </row>
-    <row r="260" spans="1:31" ht="15" customHeight="1">
+    <row r="260" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="12"/>
       <c r="B260" s="12"/>
       <c r="C260" s="12"/>
@@ -15065,7 +15058,7 @@
       <c r="AD260" s="12"/>
       <c r="AE260" s="12"/>
     </row>
-    <row r="261" spans="1:31" ht="15" customHeight="1">
+    <row r="261" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="12"/>
       <c r="B261" s="12"/>
       <c r="C261" s="12"/>
@@ -15098,7 +15091,7 @@
       <c r="AD261" s="12"/>
       <c r="AE261" s="12"/>
     </row>
-    <row r="262" spans="1:31" ht="15" customHeight="1">
+    <row r="262" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="12"/>
       <c r="B262" s="12"/>
       <c r="C262" s="12"/>
@@ -15131,7 +15124,7 @@
       <c r="AD262" s="12"/>
       <c r="AE262" s="12"/>
     </row>
-    <row r="263" spans="1:31" ht="15" customHeight="1">
+    <row r="263" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="12"/>
       <c r="B263" s="12"/>
       <c r="C263" s="12"/>
@@ -15164,7 +15157,7 @@
       <c r="AD263" s="12"/>
       <c r="AE263" s="12"/>
     </row>
-    <row r="264" spans="1:31" ht="15" customHeight="1">
+    <row r="264" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="12"/>
       <c r="B264" s="12"/>
       <c r="C264" s="12"/>
@@ -15197,7 +15190,7 @@
       <c r="AD264" s="12"/>
       <c r="AE264" s="12"/>
     </row>
-    <row r="265" spans="1:31" ht="15" customHeight="1">
+    <row r="265" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="12"/>
       <c r="B265" s="12"/>
       <c r="C265" s="12"/>
@@ -15230,7 +15223,7 @@
       <c r="AD265" s="12"/>
       <c r="AE265" s="12"/>
     </row>
-    <row r="266" spans="1:31" ht="15" customHeight="1">
+    <row r="266" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="12"/>
       <c r="B266" s="12"/>
       <c r="C266" s="12"/>
@@ -15263,7 +15256,7 @@
       <c r="AD266" s="12"/>
       <c r="AE266" s="12"/>
     </row>
-    <row r="267" spans="1:31" ht="15" customHeight="1">
+    <row r="267" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="12"/>
       <c r="B267" s="12"/>
       <c r="C267" s="12"/>
@@ -15296,7 +15289,7 @@
       <c r="AD267" s="12"/>
       <c r="AE267" s="12"/>
     </row>
-    <row r="268" spans="1:31" ht="15" customHeight="1">
+    <row r="268" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="12"/>
       <c r="B268" s="12"/>
       <c r="C268" s="12"/>
@@ -15329,7 +15322,7 @@
       <c r="AD268" s="12"/>
       <c r="AE268" s="12"/>
     </row>
-    <row r="269" spans="1:31" ht="15" customHeight="1">
+    <row r="269" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="12"/>
       <c r="B269" s="12"/>
       <c r="C269" s="12"/>
@@ -15362,7 +15355,7 @@
       <c r="AD269" s="12"/>
       <c r="AE269" s="12"/>
     </row>
-    <row r="270" spans="1:31" ht="15" customHeight="1">
+    <row r="270" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="12"/>
       <c r="B270" s="12"/>
       <c r="C270" s="12"/>
@@ -15395,7 +15388,7 @@
       <c r="AD270" s="12"/>
       <c r="AE270" s="12"/>
     </row>
-    <row r="271" spans="1:31" ht="15" customHeight="1">
+    <row r="271" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="12"/>
       <c r="B271" s="12"/>
       <c r="C271" s="12"/>
@@ -15428,7 +15421,7 @@
       <c r="AD271" s="12"/>
       <c r="AE271" s="12"/>
     </row>
-    <row r="272" spans="1:31" ht="15" customHeight="1">
+    <row r="272" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="12"/>
       <c r="B272" s="12"/>
       <c r="C272" s="12"/>
@@ -15461,7 +15454,7 @@
       <c r="AD272" s="12"/>
       <c r="AE272" s="12"/>
     </row>
-    <row r="273" spans="1:31" ht="15" customHeight="1">
+    <row r="273" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="12"/>
       <c r="B273" s="12"/>
       <c r="C273" s="12"/>
@@ -15494,7 +15487,7 @@
       <c r="AD273" s="12"/>
       <c r="AE273" s="12"/>
     </row>
-    <row r="274" spans="1:31" ht="15" customHeight="1">
+    <row r="274" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="12"/>
       <c r="B274" s="12"/>
       <c r="C274" s="12"/>
@@ -15527,7 +15520,7 @@
       <c r="AD274" s="12"/>
       <c r="AE274" s="12"/>
     </row>
-    <row r="275" spans="1:31" ht="15" customHeight="1">
+    <row r="275" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="12"/>
       <c r="B275" s="12"/>
       <c r="C275" s="12"/>
@@ -15560,7 +15553,7 @@
       <c r="AD275" s="12"/>
       <c r="AE275" s="12"/>
     </row>
-    <row r="276" spans="1:31" ht="15" customHeight="1">
+    <row r="276" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="12"/>
       <c r="B276" s="12"/>
       <c r="C276" s="12"/>
@@ -15593,7 +15586,7 @@
       <c r="AD276" s="12"/>
       <c r="AE276" s="12"/>
     </row>
-    <row r="277" spans="1:31" ht="15" customHeight="1">
+    <row r="277" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="12"/>
       <c r="B277" s="12"/>
       <c r="C277" s="12"/>
@@ -15626,7 +15619,7 @@
       <c r="AD277" s="12"/>
       <c r="AE277" s="12"/>
     </row>
-    <row r="278" spans="1:31" ht="15" customHeight="1">
+    <row r="278" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="12"/>
       <c r="B278" s="12"/>
       <c r="C278" s="12"/>
@@ -15659,7 +15652,7 @@
       <c r="AD278" s="12"/>
       <c r="AE278" s="12"/>
     </row>
-    <row r="279" spans="1:31" ht="15" customHeight="1">
+    <row r="279" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="12"/>
       <c r="B279" s="12"/>
       <c r="C279" s="12"/>
@@ -15692,7 +15685,7 @@
       <c r="AD279" s="12"/>
       <c r="AE279" s="12"/>
     </row>
-    <row r="280" spans="1:31" ht="15" customHeight="1">
+    <row r="280" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="12"/>
       <c r="B280" s="12"/>
       <c r="C280" s="12"/>
@@ -15725,7 +15718,7 @@
       <c r="AD280" s="12"/>
       <c r="AE280" s="12"/>
     </row>
-    <row r="281" spans="1:31" ht="15" customHeight="1">
+    <row r="281" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="12"/>
       <c r="B281" s="12"/>
       <c r="C281" s="12"/>
@@ -15758,7 +15751,7 @@
       <c r="AD281" s="12"/>
       <c r="AE281" s="12"/>
     </row>
-    <row r="282" spans="1:31" ht="15" customHeight="1">
+    <row r="282" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="12"/>
       <c r="B282" s="12"/>
       <c r="C282" s="12"/>
@@ -15791,7 +15784,7 @@
       <c r="AD282" s="12"/>
       <c r="AE282" s="12"/>
     </row>
-    <row r="283" spans="1:31" ht="15" customHeight="1">
+    <row r="283" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="12"/>
       <c r="B283" s="12"/>
       <c r="C283" s="12"/>
@@ -15824,7 +15817,7 @@
       <c r="AD283" s="12"/>
       <c r="AE283" s="12"/>
     </row>
-    <row r="284" spans="1:31" ht="15" customHeight="1">
+    <row r="284" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="12"/>
       <c r="B284" s="12"/>
       <c r="C284" s="12"/>
@@ -15857,7 +15850,7 @@
       <c r="AD284" s="12"/>
       <c r="AE284" s="12"/>
     </row>
-    <row r="285" spans="1:31" ht="15" customHeight="1">
+    <row r="285" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="12"/>
       <c r="B285" s="12"/>
       <c r="C285" s="12"/>
@@ -15890,7 +15883,7 @@
       <c r="AD285" s="12"/>
       <c r="AE285" s="12"/>
     </row>
-    <row r="286" spans="1:31" ht="15" customHeight="1">
+    <row r="286" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="12"/>
       <c r="B286" s="12"/>
       <c r="C286" s="12"/>
@@ -15923,7 +15916,7 @@
       <c r="AD286" s="12"/>
       <c r="AE286" s="12"/>
     </row>
-    <row r="287" spans="1:31" ht="15" customHeight="1">
+    <row r="287" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="12"/>
       <c r="B287" s="12"/>
       <c r="C287" s="12"/>
@@ -15956,7 +15949,7 @@
       <c r="AD287" s="12"/>
       <c r="AE287" s="12"/>
     </row>
-    <row r="288" spans="1:31" ht="15" customHeight="1">
+    <row r="288" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="12"/>
       <c r="B288" s="12"/>
       <c r="C288" s="12"/>
@@ -15989,7 +15982,7 @@
       <c r="AD288" s="12"/>
       <c r="AE288" s="12"/>
     </row>
-    <row r="289" spans="1:31" ht="15" customHeight="1">
+    <row r="289" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="12"/>
       <c r="B289" s="12"/>
       <c r="C289" s="12"/>
@@ -16022,7 +16015,7 @@
       <c r="AD289" s="12"/>
       <c r="AE289" s="12"/>
     </row>
-    <row r="290" spans="1:31" ht="15" customHeight="1">
+    <row r="290" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="12"/>
       <c r="B290" s="12"/>
       <c r="C290" s="12"/>
@@ -16055,7 +16048,7 @@
       <c r="AD290" s="12"/>
       <c r="AE290" s="12"/>
     </row>
-    <row r="291" spans="1:31" ht="15" customHeight="1">
+    <row r="291" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="12"/>
       <c r="B291" s="12"/>
       <c r="C291" s="12"/>
@@ -16088,7 +16081,7 @@
       <c r="AD291" s="12"/>
       <c r="AE291" s="12"/>
     </row>
-    <row r="292" spans="1:31" ht="15" customHeight="1">
+    <row r="292" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="12"/>
       <c r="B292" s="12"/>
       <c r="C292" s="12"/>
@@ -16121,7 +16114,7 @@
       <c r="AD292" s="12"/>
       <c r="AE292" s="12"/>
     </row>
-    <row r="293" spans="1:31" ht="15" customHeight="1">
+    <row r="293" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="12"/>
       <c r="B293" s="12"/>
       <c r="C293" s="12"/>
@@ -16154,7 +16147,7 @@
       <c r="AD293" s="12"/>
       <c r="AE293" s="12"/>
     </row>
-    <row r="294" spans="1:31" ht="15" customHeight="1">
+    <row r="294" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="12"/>
       <c r="B294" s="12"/>
       <c r="C294" s="12"/>
@@ -16187,7 +16180,7 @@
       <c r="AD294" s="12"/>
       <c r="AE294" s="12"/>
     </row>
-    <row r="295" spans="1:31" ht="15" customHeight="1">
+    <row r="295" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="12"/>
       <c r="B295" s="12"/>
       <c r="C295" s="12"/>
@@ -16220,7 +16213,7 @@
       <c r="AD295" s="12"/>
       <c r="AE295" s="12"/>
     </row>
-    <row r="296" spans="1:31" ht="15" customHeight="1">
+    <row r="296" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="12"/>
       <c r="B296" s="12"/>
       <c r="C296" s="12"/>
@@ -16253,7 +16246,7 @@
       <c r="AD296" s="12"/>
       <c r="AE296" s="12"/>
     </row>
-    <row r="297" spans="1:31" ht="15" customHeight="1">
+    <row r="297" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="12"/>
       <c r="B297" s="12"/>
       <c r="C297" s="12"/>
@@ -16286,7 +16279,7 @@
       <c r="AD297" s="12"/>
       <c r="AE297" s="12"/>
     </row>
-    <row r="298" spans="1:31" ht="15" customHeight="1">
+    <row r="298" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="12"/>
       <c r="B298" s="12"/>
       <c r="C298" s="12"/>
@@ -16319,7 +16312,7 @@
       <c r="AD298" s="12"/>
       <c r="AE298" s="12"/>
     </row>
-    <row r="299" spans="1:31" ht="15" customHeight="1">
+    <row r="299" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="12"/>
       <c r="B299" s="12"/>
       <c r="C299" s="12"/>
@@ -16352,7 +16345,7 @@
       <c r="AD299" s="12"/>
       <c r="AE299" s="12"/>
     </row>
-    <row r="300" spans="1:31" ht="15" customHeight="1">
+    <row r="300" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="12" t="str">
         <f>M9</f>
         <v>Sør-Afrika</v>
@@ -16403,7 +16396,7 @@
       <c r="AD300" s="12"/>
       <c r="AE300" s="12"/>
     </row>
-    <row r="301" spans="1:31" ht="15" customHeight="1">
+    <row r="301" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="12" t="str">
         <f>M17</f>
         <v>Bosnia-Hercegovina</v>
@@ -16454,7 +16447,7 @@
       <c r="AD301" s="12"/>
       <c r="AE301" s="12"/>
     </row>
-    <row r="302" spans="1:31" ht="15" customHeight="1">
+    <row r="302" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="12" t="str">
         <f>M25</f>
         <v>Skottland</v>
@@ -16505,7 +16498,7 @@
       <c r="AD302" s="12"/>
       <c r="AE302" s="12"/>
     </row>
-    <row r="303" spans="1:31" ht="15" customHeight="1">
+    <row r="303" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="12" t="str">
         <f>M33</f>
         <v>Paraguay</v>
@@ -16556,7 +16549,7 @@
       <c r="AD303" s="12"/>
       <c r="AE303" s="12"/>
     </row>
-    <row r="304" spans="1:31" ht="15" customHeight="1">
+    <row r="304" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="12" t="str">
         <f>M41</f>
         <v>Ecuador</v>
@@ -16607,7 +16600,7 @@
       <c r="AD304" s="12"/>
       <c r="AE304" s="12"/>
     </row>
-    <row r="305" spans="1:31" ht="15" customHeight="1">
+    <row r="305" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="12" t="str">
         <f>M49</f>
         <v>Tunisia</v>
@@ -16658,7 +16651,7 @@
       <c r="AD305" s="12"/>
       <c r="AE305" s="12"/>
     </row>
-    <row r="306" spans="1:31" ht="15" customHeight="1">
+    <row r="306" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="12" t="str">
         <f>M57</f>
         <v>New Zealand</v>
@@ -16709,7 +16702,7 @@
       <c r="AD306" s="12"/>
       <c r="AE306" s="12"/>
     </row>
-    <row r="307" spans="1:31" ht="15" customHeight="1">
+    <row r="307" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="12" t="str">
         <f>M65</f>
         <v>Saudi Arabia</v>
@@ -16760,7 +16753,7 @@
       <c r="AD307" s="12"/>
       <c r="AE307" s="12"/>
     </row>
-    <row r="308" spans="1:31" ht="15" customHeight="1">
+    <row r="308" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="12" t="str">
         <f>M73</f>
         <v>Norge</v>
@@ -16811,7 +16804,7 @@
       <c r="AD308" s="12"/>
       <c r="AE308" s="12"/>
     </row>
-    <row r="309" spans="1:31" ht="15" customHeight="1">
+    <row r="309" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="12" t="str">
         <f>M81</f>
         <v>Algerie</v>
@@ -16862,7 +16855,7 @@
       <c r="AD309" s="12"/>
       <c r="AE309" s="12"/>
     </row>
-    <row r="310" spans="1:31" ht="15" customHeight="1">
+    <row r="310" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="12" t="str">
         <f>M89</f>
         <v>Colombia</v>
@@ -16913,7 +16906,7 @@
       <c r="AD310" s="12"/>
       <c r="AE310" s="12"/>
     </row>
-    <row r="311" spans="1:31" ht="15" customHeight="1">
+    <row r="311" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="12" t="str">
         <f>M97</f>
         <v>Ghana</v>
@@ -16964,385 +16957,385 @@
       <c r="AD311" s="12"/>
       <c r="AE311" s="12"/>
     </row>
-    <row r="320" spans="1:31" ht="15" customHeight="1">
+    <row r="320" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B320">
         <v>28</v>
       </c>
     </row>
-    <row r="321" spans="1:2" ht="15" customHeight="1">
+    <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B321">
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:2" ht="15" customHeight="1">
+    <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B322">
         <v>27</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="15" customHeight="1">
+    <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B323">
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:2" ht="15" customHeight="1">
+    <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B324">
         <v>65</v>
       </c>
     </row>
-    <row r="325" spans="1:2" ht="15" customHeight="1">
+    <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B325">
         <v>6</v>
       </c>
     </row>
-    <row r="326" spans="1:2" ht="15" customHeight="1">
+    <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B326">
         <v>30</v>
       </c>
     </row>
-    <row r="327" spans="1:2" ht="15" customHeight="1">
+    <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B327">
         <v>13</v>
       </c>
     </row>
-    <row r="328" spans="1:2" ht="15" customHeight="1">
+    <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B328">
         <v>82</v>
       </c>
     </row>
-    <row r="329" spans="1:2" ht="15" customHeight="1">
+    <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B329">
         <v>46</v>
       </c>
     </row>
-    <row r="330" spans="1:2" ht="15" customHeight="1">
+    <row r="330" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B330">
         <v>23</v>
       </c>
     </row>
-    <row r="331" spans="1:2" ht="15" customHeight="1">
+    <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B331">
         <v>29</v>
       </c>
     </row>
-    <row r="332" spans="1:2" ht="15" customHeight="1">
+    <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B332">
         <v>34</v>
       </c>
     </row>
-    <row r="333" spans="1:2" ht="15" customHeight="1">
+    <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B333">
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:2" ht="15" customHeight="1">
+    <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B334">
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:2" ht="15" customHeight="1">
+    <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B335">
         <v>74</v>
       </c>
     </row>
-    <row r="336" spans="1:2" ht="15" customHeight="1">
+    <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B336">
         <v>83</v>
       </c>
     </row>
-    <row r="337" spans="1:2" ht="15" customHeight="1">
+    <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B337">
         <v>57</v>
       </c>
     </row>
-    <row r="338" spans="1:2" ht="15" customHeight="1">
+    <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B338">
         <v>18</v>
       </c>
     </row>
-    <row r="339" spans="1:2" ht="15" customHeight="1">
+    <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B339">
         <v>63</v>
       </c>
     </row>
-    <row r="340" spans="1:2" ht="15" customHeight="1">
+    <row r="340" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B340">
         <v>69</v>
       </c>
     </row>
-    <row r="341" spans="1:2" ht="15" customHeight="1">
+    <row r="341" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B341">
         <v>11</v>
       </c>
     </row>
-    <row r="342" spans="1:2" ht="15" customHeight="1">
+    <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B342">
         <v>67</v>
       </c>
     </row>
-    <row r="343" spans="1:2" ht="15" customHeight="1">
+    <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B343">
         <v>8</v>
       </c>
     </row>
-    <row r="344" spans="1:2" ht="15" customHeight="1">
+    <row r="344" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B344">
         <v>15</v>
       </c>
     </row>
-    <row r="345" spans="1:2" ht="15" customHeight="1">
+    <row r="345" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B345">
         <v>7</v>
       </c>
     </row>
-    <row r="346" spans="1:2" ht="15" customHeight="1">
+    <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B346">
         <v>85</v>
       </c>
     </row>
-    <row r="347" spans="1:2" ht="15" customHeight="1">
+    <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B347">
         <v>31</v>
       </c>
     </row>
-    <row r="348" spans="1:2" ht="15" customHeight="1">
+    <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B348">
         <v>33</v>
       </c>
     </row>
-    <row r="349" spans="1:2" ht="15" customHeight="1">
+    <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B349">
         <v>40</v>
       </c>
     </row>
-    <row r="350" spans="1:2" ht="15" customHeight="1">
+    <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B350">
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:2" ht="15" customHeight="1">
+    <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B351">
         <v>55</v>
       </c>
     </row>
-    <row r="352" spans="1:2" ht="15" customHeight="1">
+    <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B352">
         <v>61</v>
       </c>
     </row>
-    <row r="353" spans="1:2" ht="15" customHeight="1">
+    <row r="353" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B353">
         <v>14</v>
       </c>
     </row>
-    <row r="354" spans="1:2" ht="15" customHeight="1">
+    <row r="354" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B354">
         <v>43</v>
       </c>
     </row>
-    <row r="355" spans="1:2" ht="15" customHeight="1">
+    <row r="355" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B355">
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:2" ht="15" customHeight="1">
+    <row r="356" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B356">
         <v>19</v>
       </c>
     </row>
-    <row r="357" spans="1:2" ht="15" customHeight="1">
+    <row r="357" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B357">
         <v>38</v>
       </c>
     </row>
-    <row r="358" spans="1:2" ht="15" customHeight="1">
+    <row r="358" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B358">
         <v>60</v>
       </c>
     </row>
-    <row r="359" spans="1:2" ht="15" customHeight="1">
+    <row r="359" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B359">
         <v>25</v>
       </c>
     </row>
-    <row r="360" spans="1:2" ht="15" customHeight="1">
+    <row r="360" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B360">
         <v>41</v>
       </c>
     </row>
-    <row r="361" spans="1:2" ht="15" customHeight="1">
+    <row r="361" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B361">
         <v>44</v>
       </c>
     </row>
-    <row r="362" spans="1:2" ht="15" customHeight="1">
+    <row r="362" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B362">
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:2" ht="15" customHeight="1">
+    <row r="363" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B363">
         <v>10</v>
       </c>
     </row>
-    <row r="364" spans="1:2" ht="15" customHeight="1">
+    <row r="364" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B364">
         <v>16</v>
       </c>
     </row>
-    <row r="365" spans="1:2" ht="15" customHeight="1">
+    <row r="365" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B365">
         <v>17</v>
       </c>
     </row>
-    <row r="366" spans="1:2" ht="15" customHeight="1">
+    <row r="366" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B366">
         <v>50</v>
       </c>
     </row>
-    <row r="367" spans="1:2" ht="15" customHeight="1">
+    <row r="367" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B367">
         <v>24</v>
@@ -17499,26 +17492,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9cd4a677-7aee-4d17-8718-d38c4fab49a7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d4f56ad3-4be4-4368-a565-df4965c1e22f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100671046C6C42EE1449039E4EC9B42CCA1" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="80f13109c7168a888416f40688afc82a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9cd4a677-7aee-4d17-8718-d38c4fab49a7" xmlns:ns3="d4f56ad3-4be4-4368-a565-df4965c1e22f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="09d6a4af225531c3ac4b1ce681bc99f1" ns2:_="" ns3:_="">
     <xsd:import namespace="9cd4a677-7aee-4d17-8718-d38c4fab49a7"/>
@@ -17773,14 +17746,60 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9cd4a677-7aee-4d17-8718-d38c4fab49a7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d4f56ad3-4be4-4368-a565-df4965c1e22f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5289171D-7414-480A-A6B0-4629BA2371E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E2AB9BB-D206-4B42-BC5A-546223F1217A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9cd4a677-7aee-4d17-8718-d38c4fab49a7"/>
+    <ds:schemaRef ds:uri="d4f56ad3-4be4-4368-a565-df4965c1e22f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD46F970-DEC9-4AF4-95E8-BA2A2F98E5F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5289171D-7414-480A-A6B0-4629BA2371E5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9cd4a677-7aee-4d17-8718-d38c4fab49a7"/>
+    <ds:schemaRef ds:uri="d4f56ad3-4be4-4368-a565-df4965c1e22f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E2AB9BB-D206-4B42-BC5A-546223F1217A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD46F970-DEC9-4AF4-95E8-BA2A2F98E5F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>